--- a/tame_output/MOZAIC/bt/tame_crypto_final_trackstats_last.xlsx
+++ b/tame_output/MOZAIC/bt/tame_crypto_final_trackstats_last.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="321">
   <si>
     <t>Bitcoin</t>
   </si>
@@ -127,13 +127,13 @@
     <t>2023</t>
   </si>
   <si>
-    <t>13.6%</t>
+    <t>14.2%</t>
   </si>
   <si>
     <t>70.7%</t>
   </si>
   <si>
-    <t>0.19</t>
+    <t>0.20</t>
   </si>
   <si>
     <t>51.3%</t>
@@ -172,10 +172,10 @@
     <t>-18.8%</t>
   </si>
   <si>
-    <t>21.6%</t>
+    <t>21.0%</t>
   </si>
   <si>
-    <t>-13.1%</t>
+    <t>-13.4%</t>
   </si>
   <si>
     <t>-73.6%</t>
@@ -193,10 +193,10 @@
     <t>-64.3%</t>
   </si>
   <si>
-    <t>74.5%</t>
+    <t>79.6%</t>
   </si>
   <si>
-    <t>-14.9%</t>
+    <t>-14.6%</t>
   </si>
   <si>
     <t>87.4%</t>
@@ -229,10 +229,10 @@
     <t>-27.5%</t>
   </si>
   <si>
-    <t>27.2%</t>
+    <t>26.3%</t>
   </si>
   <si>
-    <t>-16.6%</t>
+    <t>-17.0%</t>
   </si>
   <si>
     <t>-89.3%</t>
@@ -250,10 +250,10 @@
     <t>-77.8%</t>
   </si>
   <si>
-    <t>46.4%</t>
+    <t>49.3%</t>
   </si>
   <si>
-    <t>59.0%</t>
+    <t>59.5%</t>
   </si>
   <si>
     <t>61.6%</t>
@@ -286,10 +286,10 @@
     <t>-21.1%</t>
   </si>
   <si>
-    <t>22.3%</t>
+    <t>21.7%</t>
   </si>
   <si>
-    <t>-11.9%</t>
+    <t>-12.2%</t>
   </si>
   <si>
     <t>-71.7%</t>
@@ -307,10 +307,10 @@
     <t>-50.0%</t>
   </si>
   <si>
-    <t>28.1%</t>
+    <t>30.4%</t>
   </si>
   <si>
-    <t>64.0%</t>
+    <t>64.5%</t>
   </si>
   <si>
     <t>1.19</t>
@@ -340,10 +340,10 @@
     <t>-18.3%</t>
   </si>
   <si>
-    <t>22.0%</t>
+    <t>21.4%</t>
   </si>
   <si>
-    <t>-10.7%</t>
+    <t>-11.0%</t>
   </si>
   <si>
     <t>-63.8%</t>
@@ -361,10 +361,10 @@
     <t>-49.7%</t>
   </si>
   <si>
-    <t>20.6%</t>
+    <t>22.6%</t>
   </si>
   <si>
-    <t>125.0%</t>
+    <t>124.9%</t>
   </si>
   <si>
     <t>46.1%</t>
@@ -382,7 +382,7 @@
     <t>50.9%</t>
   </si>
   <si>
-    <t>34.6%</t>
+    <t>34.7%</t>
   </si>
   <si>
     <t>2023-02-03</t>
@@ -397,7 +397,7 @@
     <t>-12.7%</t>
   </si>
   <si>
-    <t>-7.8%</t>
+    <t>-7.9%</t>
   </si>
   <si>
     <t>14.8%</t>
@@ -421,7 +421,7 @@
     <t>124.8%</t>
   </si>
   <si>
-    <t>-14.4%</t>
+    <t>-14.5%</t>
   </si>
   <si>
     <t>92.0%</t>
@@ -481,6 +481,9 @@
     <t>71.8%</t>
   </si>
   <si>
+    <t>28.1%</t>
+  </si>
+  <si>
     <t>2.56</t>
   </si>
   <si>
@@ -533,6 +536,9 @@
   </si>
   <si>
     <t>145.4%</t>
+  </si>
+  <si>
+    <t>13.6%</t>
   </si>
   <si>
     <t>23.7%</t>
@@ -679,9 +685,6 @@
     <t>-13.7%</t>
   </si>
   <si>
-    <t>-12.2%</t>
-  </si>
-  <si>
     <t>18.9%</t>
   </si>
   <si>
@@ -703,7 +706,7 @@
     <t>42.7%</t>
   </si>
   <si>
-    <t>125.8%</t>
+    <t>125.9%</t>
   </si>
   <si>
     <t>46.0%</t>
@@ -731,9 +734,6 @@
   </si>
   <si>
     <t>18.1%</t>
-  </si>
-  <si>
-    <t>-7.9%</t>
   </si>
   <si>
     <t>153.6%</t>
@@ -784,7 +784,7 @@
     <t>1.1</t>
   </si>
   <si>
-    <t>-23.9%</t>
+    <t>-24.0%</t>
   </si>
   <si>
     <t>37.6%</t>
@@ -799,7 +799,7 @@
     <t>118.5%</t>
   </si>
   <si>
-    <t>107.8%</t>
+    <t>107.6%</t>
   </si>
   <si>
     <t>0.6</t>
@@ -814,10 +814,10 @@
     <t>0.7</t>
   </si>
   <si>
-    <t>59.5%</t>
+    <t>59.4%</t>
   </si>
   <si>
-    <t>80.5%</t>
+    <t>80.4%</t>
   </si>
   <si>
     <t>0.5</t>
@@ -835,10 +835,10 @@
     <t>48.1%</t>
   </si>
   <si>
-    <t>-0.0</t>
+    <t>70.6%</t>
   </si>
   <si>
-    <t>126.0%</t>
+    <t>-0.0</t>
   </si>
   <si>
     <t>38.6%</t>
@@ -856,7 +856,7 @@
     <t>0.4</t>
   </si>
   <si>
-    <t>72.4%</t>
+    <t>72.1%</t>
   </si>
   <si>
     <t>2.2</t>
@@ -865,7 +865,7 @@
     <t>26.2%</t>
   </si>
   <si>
-    <t>58.3%</t>
+    <t>58.2%</t>
   </si>
   <si>
     <t>0.1</t>
@@ -883,13 +883,10 @@
     <t>0.2</t>
   </si>
   <si>
-    <t>-11.6%</t>
+    <t>18.5%</t>
   </si>
   <si>
-    <t>18.4%</t>
-  </si>
-  <si>
-    <t>18.0%</t>
+    <t>17.9%</t>
   </si>
   <si>
     <t>24.9%</t>
@@ -898,13 +895,10 @@
     <t>0.3</t>
   </si>
   <si>
-    <t>0.9%</t>
+    <t>13.9%</t>
   </si>
   <si>
-    <t>13.8%</t>
-  </si>
-  <si>
-    <t>85.5%</t>
+    <t>85.2%</t>
   </si>
   <si>
     <t>32.6%</t>
@@ -913,13 +907,10 @@
     <t>2.6</t>
   </si>
   <si>
-    <t>24.8%</t>
+    <t>60.8%</t>
   </si>
   <si>
-    <t>60.9%</t>
-  </si>
-  <si>
-    <t>92.9%</t>
+    <t>92.4%</t>
   </si>
   <si>
     <t>30.8%</t>
@@ -934,19 +925,16 @@
     <t>65.0%</t>
   </si>
   <si>
-    <t>100.7%</t>
+    <t>100.2%</t>
   </si>
   <si>
     <t>29.1%</t>
   </si>
   <si>
-    <t>3.5</t>
+    <t>3.4</t>
   </si>
   <si>
-    <t>24.1%</t>
-  </si>
-  <si>
-    <t>64.1%</t>
+    <t>64.0%</t>
   </si>
   <si>
     <t>name</t>
@@ -1419,16 +1407,16 @@
         <v>153</v>
       </c>
       <c r="I2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1454,19 +1442,19 @@
         <v>136</v>
       </c>
       <c r="H3" t="s">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="I3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1492,19 +1480,19 @@
         <v>137</v>
       </c>
       <c r="H4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1530,16 +1518,16 @@
         <v>138</v>
       </c>
       <c r="H5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L5" t="s">
         <v>118</v>
@@ -1682,16 +1670,16 @@
         <v>139</v>
       </c>
       <c r="H9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L9" t="s">
         <v>139</v>
@@ -1720,19 +1708,19 @@
         <v>140</v>
       </c>
       <c r="H10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1758,19 +1746,19 @@
         <v>141</v>
       </c>
       <c r="H11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1796,10 +1784,10 @@
         <v>45</v>
       </c>
       <c r="H12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J12" t="s">
         <v>45</v>
@@ -1834,10 +1822,10 @@
         <v>142</v>
       </c>
       <c r="H13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I13" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J13" t="s">
         <v>142</v>
@@ -1869,16 +1857,16 @@
         <v>143</v>
       </c>
       <c r="H14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J14" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K14" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1942,19 +1930,19 @@
         <v>144</v>
       </c>
       <c r="H16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I16" t="s">
         <v>50</v>
       </c>
       <c r="J16" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K16" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1980,19 +1968,19 @@
         <v>145</v>
       </c>
       <c r="H17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I17" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J17" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K17" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L17" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -2018,19 +2006,19 @@
         <v>146</v>
       </c>
       <c r="H18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J18" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K18" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="L18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -2056,19 +2044,19 @@
         <v>147</v>
       </c>
       <c r="H19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I19" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J19" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K19" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -2094,19 +2082,19 @@
         <v>148</v>
       </c>
       <c r="H20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I20" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J20" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K20" t="s">
         <v>148</v>
       </c>
       <c r="L20" t="s">
-        <v>238</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -2132,16 +2120,16 @@
         <v>113</v>
       </c>
       <c r="H21" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I21" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J21" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K21" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L21" t="s">
         <v>113</v>
@@ -2170,16 +2158,16 @@
         <v>149</v>
       </c>
       <c r="H22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I22" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J22" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L22" t="s">
         <v>239</v>
@@ -2208,16 +2196,16 @@
         <v>150</v>
       </c>
       <c r="H23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I23" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J23" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K23" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L23" t="s">
         <v>240</v>
@@ -2246,16 +2234,16 @@
         <v>151</v>
       </c>
       <c r="H24" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J24" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K24" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L24" t="s">
         <v>241</v>
@@ -2284,16 +2272,16 @@
         <v>125</v>
       </c>
       <c r="H25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I25" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J25" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K25" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L25" t="s">
         <v>242</v>
@@ -2322,16 +2310,16 @@
         <v>152</v>
       </c>
       <c r="H26" t="s">
-        <v>36</v>
+        <v>173</v>
       </c>
       <c r="I26" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J26" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K26" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L26" t="s">
         <v>243</v>
@@ -2408,16 +2396,16 @@
         <v>153</v>
       </c>
       <c r="I2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2443,19 +2431,19 @@
         <v>136</v>
       </c>
       <c r="H3" t="s">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="I3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2481,19 +2469,19 @@
         <v>137</v>
       </c>
       <c r="H4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2519,16 +2507,16 @@
         <v>138</v>
       </c>
       <c r="H5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L5" t="s">
         <v>118</v>
@@ -2671,16 +2659,16 @@
         <v>139</v>
       </c>
       <c r="H9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L9" t="s">
         <v>139</v>
@@ -2709,19 +2697,19 @@
         <v>140</v>
       </c>
       <c r="H10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2747,19 +2735,19 @@
         <v>141</v>
       </c>
       <c r="H11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2785,10 +2773,10 @@
         <v>45</v>
       </c>
       <c r="H12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J12" t="s">
         <v>45</v>
@@ -2823,10 +2811,10 @@
         <v>142</v>
       </c>
       <c r="H13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I13" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J13" t="s">
         <v>142</v>
@@ -2858,16 +2846,16 @@
         <v>143</v>
       </c>
       <c r="H14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J14" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K14" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2931,19 +2919,19 @@
         <v>144</v>
       </c>
       <c r="H16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I16" t="s">
         <v>50</v>
       </c>
       <c r="J16" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K16" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -2969,19 +2957,19 @@
         <v>145</v>
       </c>
       <c r="H17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I17" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J17" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K17" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L17" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -3007,19 +2995,19 @@
         <v>146</v>
       </c>
       <c r="H18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J18" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K18" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="L18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -3045,19 +3033,19 @@
         <v>147</v>
       </c>
       <c r="H19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I19" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J19" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K19" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -3083,19 +3071,19 @@
         <v>148</v>
       </c>
       <c r="H20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I20" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J20" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K20" t="s">
         <v>148</v>
       </c>
       <c r="L20" t="s">
-        <v>238</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -3115,7 +3103,7 @@
         <v>267</v>
       </c>
       <c r="F21" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G21" t="s">
         <v>278</v>
@@ -3141,7 +3129,7 @@
         <v>245</v>
       </c>
       <c r="B22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C22" t="s">
         <v>255</v>
@@ -3153,7 +3141,7 @@
         <v>268</v>
       </c>
       <c r="F22" t="s">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="G22" t="s">
         <v>279</v>
@@ -3162,16 +3150,16 @@
         <v>284</v>
       </c>
       <c r="I22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J22" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K22" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L22" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -3179,7 +3167,7 @@
         <v>246</v>
       </c>
       <c r="B23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C23" t="s">
         <v>256</v>
@@ -3194,22 +3182,22 @@
         <v>274</v>
       </c>
       <c r="G23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H23" t="s">
         <v>285</v>
       </c>
       <c r="I23" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J23" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="K23" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="L23" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -3241,13 +3229,13 @@
         <v>264</v>
       </c>
       <c r="J24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K24" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="L24" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -3267,7 +3255,7 @@
         <v>261</v>
       </c>
       <c r="F25" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G25" t="s">
         <v>261</v>
@@ -3276,7 +3264,7 @@
         <v>287</v>
       </c>
       <c r="I25" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J25" t="s">
         <v>261</v>
@@ -3311,19 +3299,19 @@
         <v>281</v>
       </c>
       <c r="H26" t="s">
-        <v>288</v>
+        <v>237</v>
       </c>
       <c r="I26" t="s">
-        <v>293</v>
+        <v>191</v>
       </c>
       <c r="J26" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="K26" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="L26" t="s">
-        <v>308</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -3340,7 +3328,7 @@
         <v>266</v>
       </c>
       <c r="E27" t="s">
-        <v>37</v>
+        <v>272</v>
       </c>
       <c r="F27" t="s">
         <v>277</v>
@@ -3349,19 +3337,19 @@
         <v>282</v>
       </c>
       <c r="H27" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I27" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J27" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="K27" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="L27" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -3387,16 +3375,16 @@
         <v>113</v>
       </c>
       <c r="H28" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I28" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J28" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K28" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L28" t="s">
         <v>113</v>
@@ -3425,16 +3413,16 @@
         <v>149</v>
       </c>
       <c r="H29" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I29" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J29" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K29" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L29" t="s">
         <v>239</v>
@@ -3463,16 +3451,16 @@
         <v>150</v>
       </c>
       <c r="H30" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I30" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J30" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K30" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L30" t="s">
         <v>240</v>
@@ -3501,16 +3489,16 @@
         <v>151</v>
       </c>
       <c r="H31" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I31" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J31" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K31" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L31" t="s">
         <v>241</v>
@@ -3539,16 +3527,16 @@
         <v>125</v>
       </c>
       <c r="H32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I32" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J32" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K32" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L32" t="s">
         <v>242</v>
@@ -3577,16 +3565,16 @@
         <v>152</v>
       </c>
       <c r="H33" t="s">
-        <v>36</v>
+        <v>173</v>
       </c>
       <c r="I33" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J33" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K33" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L33" t="s">
         <v>243</v>
@@ -75474,10 +75462,10 @@
         <v>16.75368870367502</v>
       </c>
       <c r="F1892">
-        <v>111.4424146724051</v>
+        <v>111.4516980422553</v>
       </c>
       <c r="G1892">
-        <v>36.66560323337283</v>
+        <v>36.66661927204106</v>
       </c>
       <c r="H1892">
         <v>17.58382230070274</v>
@@ -75486,13 +75474,13 @@
         <v>2.5335620318396</v>
       </c>
       <c r="J1892">
-        <v>53.93350354279506</v>
+        <v>53.9349240718109</v>
       </c>
       <c r="K1892">
-        <v>63.93466286931894</v>
+        <v>63.93643688267819</v>
       </c>
       <c r="L1892">
-        <v>77.13819273059518</v>
+        <v>77.14012000959137</v>
       </c>
     </row>
     <row r="1893" spans="1:12">
@@ -75503,7 +75491,7 @@
         <v>1.583517212211019</v>
       </c>
       <c r="C1893">
-        <v>0.3886976224402621</v>
+        <v>0.3885710230831014</v>
       </c>
       <c r="D1893">
         <v>13.30833131958303</v>
@@ -75512,10 +75500,10 @@
         <v>16.73858326184065</v>
       </c>
       <c r="F1893">
-        <v>110.7895292289114</v>
+        <v>110.8114325043231</v>
       </c>
       <c r="G1893">
-        <v>36.57637440721926</v>
+        <v>36.57877788314443</v>
       </c>
       <c r="H1893">
         <v>17.55312255163953</v>
@@ -75524,13 +75512,13 @@
         <v>2.54419829614099</v>
       </c>
       <c r="J1893">
-        <v>53.78527367216803</v>
+        <v>53.78863256633612</v>
       </c>
       <c r="K1893">
-        <v>63.91327603246982</v>
+        <v>63.91747307057593</v>
       </c>
       <c r="L1893">
-        <v>77.08130046487857</v>
+        <v>77.08585803582586</v>
       </c>
     </row>
     <row r="1894" spans="1:12">
@@ -75541,7 +75529,7 @@
         <v>1.56853421401034</v>
       </c>
       <c r="C1894">
-        <v>0.3839468983684847</v>
+        <v>0.383821846328773</v>
       </c>
       <c r="D1894">
         <v>13.17022253974023</v>
@@ -75550,10 +75538,10 @@
         <v>16.55458071001329</v>
       </c>
       <c r="F1894">
-        <v>110.8821898456887</v>
+        <v>110.9041114402595</v>
       </c>
       <c r="G1894">
-        <v>36.32818915324135</v>
+        <v>36.33057632062604</v>
       </c>
       <c r="H1894">
         <v>17.51979423943467</v>
@@ -75562,13 +75550,13 @@
         <v>2.544953495105777</v>
       </c>
       <c r="J1894">
-        <v>53.41303623667903</v>
+        <v>53.41637188459278</v>
       </c>
       <c r="K1894">
-        <v>63.4890847701439</v>
+        <v>63.49325395258366</v>
       </c>
       <c r="L1894">
-        <v>76.5842831976888</v>
+        <v>76.58881138159354</v>
       </c>
     </row>
     <row r="1895" spans="1:12">
@@ -75579,7 +75567,7 @@
         <v>1.533732165935455</v>
       </c>
       <c r="C1895">
-        <v>0.3671977854438976</v>
+        <v>0.3670781886136003</v>
       </c>
       <c r="D1895">
         <v>12.82965614621331</v>
@@ -75588,10 +75576,10 @@
         <v>16.37533776950976</v>
       </c>
       <c r="F1895">
-        <v>113.2463546528931</v>
+        <v>113.2687436468043</v>
       </c>
       <c r="G1895">
-        <v>36.14213070927923</v>
+        <v>36.14450565054807</v>
       </c>
       <c r="H1895">
         <v>17.33336467588943</v>
@@ -75600,13 +75588,13 @@
         <v>2.573977822371175</v>
       </c>
       <c r="J1895">
-        <v>53.01106093213748</v>
+        <v>53.01437147666486</v>
       </c>
       <c r="K1895">
-        <v>63.52595477740731</v>
+        <v>63.53012638101576</v>
       </c>
       <c r="L1895">
-        <v>76.4205755942493</v>
+        <v>76.42509409864665</v>
       </c>
     </row>
     <row r="1896" spans="1:12">
@@ -75617,7 +75605,7 @@
         <v>1.438818645641565</v>
       </c>
       <c r="C1896">
-        <v>0.3505870607119906</v>
+        <v>0.3504728740178805</v>
       </c>
       <c r="D1896">
         <v>12.19451637890514</v>
@@ -75626,10 +75614,10 @@
         <v>15.97682722856588</v>
       </c>
       <c r="F1896">
-        <v>110.9787343637809</v>
+        <v>111.0006750453645</v>
       </c>
       <c r="G1896">
-        <v>35.01183433452213</v>
+        <v>35.01413500270706</v>
       </c>
       <c r="H1896">
         <v>16.85287889435073</v>
@@ -75638,13 +75626,13 @@
         <v>2.533121183061445</v>
       </c>
       <c r="J1896">
-        <v>51.0687335862758</v>
+        <v>51.07192283232222</v>
       </c>
       <c r="K1896">
-        <v>61.03509387685245</v>
+        <v>61.03910191134403</v>
       </c>
       <c r="L1896">
-        <v>73.19416100546984</v>
+        <v>73.19848874228407</v>
       </c>
     </row>
     <row r="1897" spans="1:12">
@@ -75655,7 +75643,7 @@
         <v>1.423871684646518</v>
       </c>
       <c r="C1897">
-        <v>0.3513248076577424</v>
+        <v>0.3512103806784242</v>
       </c>
       <c r="D1897">
         <v>12.03887620024141</v>
@@ -75664,10 +75652,10 @@
         <v>15.95520621018151</v>
       </c>
       <c r="F1897">
-        <v>108.0719012111761</v>
+        <v>108.0932672069788</v>
       </c>
       <c r="G1897">
-        <v>34.54140241908305</v>
+        <v>34.54367217464197</v>
       </c>
       <c r="H1897">
         <v>17.0713665969956</v>
@@ -75676,13 +75664,13 @@
         <v>2.495247949392769</v>
       </c>
       <c r="J1897">
-        <v>50.5823832226795</v>
+        <v>50.58554209611111</v>
       </c>
       <c r="K1897">
-        <v>59.75872951493512</v>
+        <v>59.7626537335093</v>
       </c>
       <c r="L1897">
-        <v>72.05381983716366</v>
+        <v>72.05808014924911</v>
       </c>
     </row>
     <row r="1898" spans="1:12">
@@ -75693,7 +75681,7 @@
         <v>1.445426173286092</v>
       </c>
       <c r="C1898">
-        <v>0.347170648770436</v>
+        <v>0.347057574806455</v>
       </c>
       <c r="D1898">
         <v>11.77493867157389</v>
@@ -75702,10 +75690,10 @@
         <v>15.91240928232163</v>
       </c>
       <c r="F1898">
-        <v>106.6829290937405</v>
+        <v>106.7040204874302</v>
       </c>
       <c r="G1898">
-        <v>34.11190510673848</v>
+        <v>34.11414663953156</v>
       </c>
       <c r="H1898">
         <v>17.16818352907954</v>
@@ -75714,13 +75702,13 @@
         <v>2.528384958271981</v>
       </c>
       <c r="J1898">
-        <v>50.05659273541817</v>
+        <v>50.05971877319644</v>
       </c>
       <c r="K1898">
-        <v>59.41247236554986</v>
+        <v>59.41637384621198</v>
       </c>
       <c r="L1898">
-        <v>71.78023143690815</v>
+        <v>71.78447557258586</v>
       </c>
     </row>
     <row r="1899" spans="1:12">
@@ -75731,7 +75719,7 @@
         <v>1.554341914497954</v>
       </c>
       <c r="C1899">
-        <v>0.3767962568507113</v>
+        <v>0.3766735337849043</v>
       </c>
       <c r="D1899">
         <v>12.37384958433096</v>
@@ -75740,10 +75728,10 @@
         <v>16.109979173084</v>
       </c>
       <c r="F1899">
-        <v>103.0044362852641</v>
+        <v>103.0248004347671</v>
       </c>
       <c r="G1899">
-        <v>34.43936419710769</v>
+        <v>34.44162724761687</v>
       </c>
       <c r="H1899">
         <v>17.746386989442</v>
@@ -75752,13 +75740,13 @@
         <v>2.529389401790736</v>
       </c>
       <c r="J1899">
-        <v>50.93454890556995</v>
+        <v>50.93772977177353</v>
       </c>
       <c r="K1899">
-        <v>59.99460693163015</v>
+        <v>59.99854663973277</v>
       </c>
       <c r="L1899">
-        <v>73.0175836499094</v>
+        <v>73.02190094626893</v>
       </c>
     </row>
     <row r="1900" spans="1:12">
@@ -75769,7 +75757,7 @@
         <v>1.703887131919062</v>
       </c>
       <c r="C1900">
-        <v>0.3933167590354432</v>
+        <v>0.3931886552190584</v>
       </c>
       <c r="D1900">
         <v>12.78040538690041</v>
@@ -75778,10 +75766,10 @@
         <v>16.31908486397946</v>
       </c>
       <c r="F1900">
-        <v>101.8903945143171</v>
+        <v>101.9105384158968</v>
       </c>
       <c r="G1900">
-        <v>34.84292230240705</v>
+        <v>34.84521187118673</v>
       </c>
       <c r="H1900">
         <v>17.82117556914881</v>
@@ -75790,13 +75778,13 @@
         <v>2.690962762231197</v>
       </c>
       <c r="J1900">
-        <v>51.55521742921959</v>
+        <v>51.55843705621663</v>
       </c>
       <c r="K1900">
-        <v>62.61379951453412</v>
+        <v>62.61791121900056</v>
       </c>
       <c r="L1900">
-        <v>75.96347770920697</v>
+        <v>75.96796918686725</v>
       </c>
     </row>
     <row r="1901" spans="1:12">
@@ -75807,7 +75795,7 @@
         <v>1.743240467081788</v>
       </c>
       <c r="C1901">
-        <v>0.4051373018012822</v>
+        <v>0.4050053480176501</v>
       </c>
       <c r="D1901">
         <v>12.98999650182257</v>
@@ -75816,10 +75804,10 @@
         <v>16.56309894353928</v>
       </c>
       <c r="F1901">
-        <v>100.3252604680722</v>
+        <v>100.3450949400305</v>
       </c>
       <c r="G1901">
-        <v>35.02864825313058</v>
+        <v>35.03095002617759</v>
       </c>
       <c r="H1901">
         <v>17.27599091341336</v>
@@ -75828,13 +75816,13 @@
         <v>2.712366826142702</v>
       </c>
       <c r="J1901">
-        <v>51.4219920296464</v>
+        <v>51.42520333670777</v>
       </c>
       <c r="K1901">
-        <v>63.19657152197703</v>
+        <v>63.20072149574328</v>
       </c>
       <c r="L1901">
-        <v>76.01883041334712</v>
+        <v>76.02332516383589</v>
       </c>
     </row>
     <row r="1902" spans="1:12">
@@ -75845,7 +75833,7 @@
         <v>1.716053575185394</v>
       </c>
       <c r="C1902">
-        <v>0.3768823791486253</v>
+        <v>0.3767596280326659</v>
       </c>
       <c r="D1902">
         <v>12.46359811893264</v>
@@ -75854,10 +75842,10 @@
         <v>15.89511377752104</v>
       </c>
       <c r="F1902">
-        <v>102.7778677242771</v>
+        <v>102.798187080796</v>
       </c>
       <c r="G1902">
-        <v>34.37003342196716</v>
+        <v>34.3722919166708</v>
       </c>
       <c r="H1902">
         <v>17.34073626699063</v>
@@ -75866,13 +75854,13 @@
         <v>2.794622455942442</v>
       </c>
       <c r="J1902">
-        <v>50.55166756322607</v>
+        <v>50.55482451846257</v>
       </c>
       <c r="K1902">
-        <v>62.96659261987035</v>
+        <v>62.97072749145007</v>
       </c>
       <c r="L1902">
-        <v>75.84107809748328</v>
+        <v>75.8455623380457</v>
       </c>
     </row>
     <row r="1903" spans="1:12">
@@ -75883,7 +75871,7 @@
         <v>1.766443481226086</v>
       </c>
       <c r="C1903">
-        <v>0.3853272757346251</v>
+        <v>0.3852017741040822</v>
       </c>
       <c r="D1903">
         <v>12.8424014492978</v>
@@ -75892,10 +75880,10 @@
         <v>16.23695964921132</v>
       </c>
       <c r="F1903">
-        <v>103.5664489488318</v>
+        <v>103.5869242091792</v>
       </c>
       <c r="G1903">
-        <v>35.08293106212989</v>
+        <v>35.08523640216315</v>
       </c>
       <c r="H1903">
         <v>17.42128071699801</v>
@@ -75904,13 +75892,13 @@
         <v>2.810157002621854</v>
       </c>
       <c r="J1903">
-        <v>51.60647604319576</v>
+        <v>51.60969887129689</v>
       </c>
       <c r="K1903">
-        <v>64.44764252467554</v>
+        <v>64.45187465340234</v>
       </c>
       <c r="L1903">
-        <v>77.53463091734689</v>
+        <v>77.53921529227502</v>
       </c>
     </row>
     <row r="1904" spans="1:12">
@@ -75921,7 +75909,7 @@
         <v>1.935772417927643</v>
       </c>
       <c r="C1904">
-        <v>0.4134884076317031</v>
+        <v>0.4133537338812674</v>
       </c>
       <c r="D1904">
         <v>13.60160456529339</v>
@@ -75930,10 +75918,10 @@
         <v>17.14363737478056</v>
       </c>
       <c r="F1904">
-        <v>101.6349945542184</v>
+        <v>101.6637202064824</v>
       </c>
       <c r="G1904">
-        <v>36.41028161255901</v>
+        <v>36.41267417433427</v>
       </c>
       <c r="H1904">
         <v>17.86713277953596</v>
@@ -75942,13 +75930,13 @@
         <v>2.913740633979805</v>
       </c>
       <c r="J1904">
-        <v>53.79154669539631</v>
+        <v>53.79490598131515</v>
       </c>
       <c r="K1904">
-        <v>68.07378108606281</v>
+        <v>68.0782513349841</v>
       </c>
       <c r="L1904">
-        <v>81.9569335776937</v>
+        <v>81.96177942924467</v>
       </c>
     </row>
     <row r="1905" spans="1:12">
@@ -75959,7 +75947,7 @@
         <v>1.901315196447831</v>
       </c>
       <c r="C1905">
-        <v>0.3996314345302357</v>
+        <v>0.3998041267808601</v>
       </c>
       <c r="D1905">
         <v>13.26867713180591</v>
@@ -75968,10 +75956,10 @@
         <v>16.72458280917756</v>
       </c>
       <c r="F1905">
-        <v>101.6880897549922</v>
+        <v>101.5841170798784</v>
       </c>
       <c r="G1905">
-        <v>35.64227050490888</v>
+        <v>35.64461259978474</v>
       </c>
       <c r="H1905">
         <v>17.78478584869487</v>
@@ -75980,13 +75968,13 @@
         <v>2.952467042179885</v>
       </c>
       <c r="J1905">
-        <v>52.65166088193795</v>
+        <v>52.65494898190664</v>
       </c>
       <c r="K1905">
-        <v>67.09026685182235</v>
+        <v>67.09467251562182</v>
       </c>
       <c r="L1905">
-        <v>80.79681645152124</v>
+        <v>80.80159370905423</v>
       </c>
     </row>
     <row r="1906" spans="1:12">
@@ -75997,7 +75985,7 @@
         <v>1.976596212402555</v>
       </c>
       <c r="C1906">
-        <v>0.4084092248667901</v>
+        <v>0.4085857102533836</v>
       </c>
       <c r="D1906">
         <v>13.58025326293618</v>
@@ -76006,10 +75994,10 @@
         <v>17.1008319266492</v>
       </c>
       <c r="F1906">
-        <v>102.4629066348591</v>
+        <v>102.3581417353666</v>
       </c>
       <c r="G1906">
-        <v>36.06376754017469</v>
+        <v>36.06613733210892</v>
       </c>
       <c r="H1906">
         <v>17.7249439011885</v>
@@ -76018,13 +76006,13 @@
         <v>3.012467534683963</v>
       </c>
       <c r="J1906">
-        <v>53.19888427482977</v>
+        <v>53.20220654893829</v>
       </c>
       <c r="K1906">
-        <v>68.56536982809818</v>
+        <v>68.5698723585236</v>
       </c>
       <c r="L1906">
-        <v>82.32767053297698</v>
+        <v>82.33253830501926</v>
       </c>
     </row>
     <row r="1907" spans="1:12">
@@ -76035,7 +76023,7 @@
         <v>1.958516840964969</v>
       </c>
       <c r="C1907">
-        <v>0.3904951024835792</v>
+        <v>0.3906638466620371</v>
       </c>
       <c r="D1907">
         <v>13.2531172775303</v>
@@ -76044,10 +76032,10 @@
         <v>16.71390425472369</v>
       </c>
       <c r="F1907">
-        <v>103.4873289438602</v>
+        <v>103.3815166067753</v>
       </c>
       <c r="G1907">
-        <v>35.54302494107767</v>
+        <v>35.54536051441259</v>
       </c>
       <c r="H1907">
         <v>17.61969693893087</v>
@@ -76056,13 +76044,13 @@
         <v>3.072852234389106</v>
       </c>
       <c r="J1907">
-        <v>52.39015656481251</v>
+        <v>52.39342833381798</v>
       </c>
       <c r="K1907">
-        <v>68.26251450421677</v>
+        <v>68.26699714682834</v>
       </c>
       <c r="L1907">
-        <v>81.87818002368759</v>
+        <v>81.88302121879261</v>
       </c>
     </row>
     <row r="1908" spans="1:12">
@@ -76073,7 +76061,7 @@
         <v>1.985965885867044</v>
       </c>
       <c r="C1908">
-        <v>0.4106691918928862</v>
+        <v>0.4108466538763098</v>
       </c>
       <c r="D1908">
         <v>13.50003495509383</v>
@@ -76082,10 +76070,10 @@
         <v>17.00188895934852</v>
       </c>
       <c r="F1908">
-        <v>101.6083135446749</v>
+        <v>101.5044224380714</v>
       </c>
       <c r="G1908">
-        <v>36.54245177834618</v>
+        <v>36.54485302517611</v>
       </c>
       <c r="H1908">
         <v>17.83499985036857</v>
@@ -76094,13 +76082,13 @@
         <v>2.927516600784457</v>
       </c>
       <c r="J1908">
-        <v>53.94969161551929</v>
+        <v>53.95306077759965</v>
       </c>
       <c r="K1908">
-        <v>68.56767946491721</v>
+        <v>68.57218214701116</v>
       </c>
       <c r="L1908">
-        <v>82.45773644129372</v>
+        <v>82.46261190371747</v>
       </c>
     </row>
     <row r="1909" spans="1:12">
@@ -76111,7 +76099,7 @@
         <v>1.925585901135481</v>
       </c>
       <c r="C1909">
-        <v>0.3948600374773516</v>
+        <v>0.3950306678699129</v>
       </c>
       <c r="D1909">
         <v>12.84537800149772</v>
@@ -76120,10 +76108,10 @@
         <v>16.17798339179531</v>
       </c>
       <c r="F1909">
-        <v>97.73091537835896</v>
+        <v>97.63098878186483</v>
       </c>
       <c r="G1909">
-        <v>34.88496508279575</v>
+        <v>34.88725741425522</v>
       </c>
       <c r="H1909">
         <v>17.47159876871271</v>
@@ -76132,13 +76120,13 @@
         <v>2.958817483037291</v>
       </c>
       <c r="J1909">
-        <v>51.35018614651259</v>
+        <v>51.35339296929143</v>
       </c>
       <c r="K1909">
-        <v>65.82415895093234</v>
+        <v>65.82848147233267</v>
       </c>
       <c r="L1909">
-        <v>79.06834356835445</v>
+        <v>79.07301862681001</v>
       </c>
     </row>
     <row r="1910" spans="1:12">
@@ -76149,7 +76137,7 @@
         <v>1.999387271823641</v>
       </c>
       <c r="C1910">
-        <v>0.4090720940151929</v>
+        <v>0.4092488658466336</v>
       </c>
       <c r="D1910">
         <v>13.3204243447804</v>
@@ -76158,10 +76146,10 @@
         <v>16.77149920356796</v>
       </c>
       <c r="F1910">
-        <v>97.95452179328058</v>
+        <v>97.85436656669634</v>
       </c>
       <c r="G1910">
-        <v>35.97838586330439</v>
+        <v>35.98075004470975</v>
       </c>
       <c r="H1910">
         <v>17.40441827710914</v>
@@ -76170,13 +76158,13 @@
         <v>2.953766324523639</v>
       </c>
       <c r="J1910">
-        <v>52.82984942141783</v>
+        <v>52.83314864927348</v>
       </c>
       <c r="K1910">
-        <v>67.83113978948013</v>
+        <v>67.83559410470453</v>
       </c>
       <c r="L1910">
-        <v>81.16205346944642</v>
+        <v>81.16685232227701</v>
       </c>
     </row>
     <row r="1911" spans="1:12">
@@ -76187,7 +76175,7 @@
         <v>1.939965452794783</v>
       </c>
       <c r="C1911">
-        <v>0.3930801929905262</v>
+        <v>0.3932500542610324</v>
       </c>
       <c r="D1911">
         <v>12.87051495706513</v>
@@ -76196,10 +76184,10 @@
         <v>16.20502663914841</v>
       </c>
       <c r="F1911">
-        <v>98.31399622194748</v>
+        <v>98.21347344476736</v>
       </c>
       <c r="G1911">
-        <v>35.35499766234216</v>
+        <v>35.35732088018683</v>
       </c>
       <c r="H1911">
         <v>17.34947623768245</v>
@@ -76208,13 +76196,13 @@
         <v>2.981388174049924</v>
       </c>
       <c r="J1911">
-        <v>51.91855557694787</v>
+        <v>51.92179789443809</v>
       </c>
       <c r="K1911">
-        <v>66.97300519694569</v>
+        <v>66.9774031604415</v>
       </c>
       <c r="L1911">
-        <v>80.17389455665513</v>
+        <v>80.17863498280732</v>
       </c>
     </row>
     <row r="1912" spans="1:12">
@@ -76225,7 +76213,7 @@
         <v>1.940564659664909</v>
       </c>
       <c r="C1912">
-        <v>0.3889629650494424</v>
+        <v>0.3891310471471958</v>
       </c>
       <c r="D1912">
         <v>12.90913413873592</v>
@@ -76234,10 +76222,10 @@
         <v>16.25365133441856</v>
       </c>
       <c r="F1912">
-        <v>99.66920652712679</v>
+        <v>99.56729809267746</v>
       </c>
       <c r="G1912">
-        <v>35.61557646025381</v>
+        <v>35.61791680103309</v>
       </c>
       <c r="H1912">
         <v>17.20484539401573</v>
@@ -76246,13 +76234,13 @@
         <v>3.015983654443071</v>
       </c>
       <c r="J1912">
-        <v>52.17387826690257</v>
+        <v>52.17713652931294</v>
       </c>
       <c r="K1912">
-        <v>67.85519107931435</v>
+        <v>67.85964697393175</v>
       </c>
       <c r="L1912">
-        <v>80.95726997386963</v>
+        <v>80.9620567185066</v>
       </c>
     </row>
     <row r="1913" spans="1:12">
@@ -76263,7 +76251,7 @@
         <v>1.976255625478732</v>
       </c>
       <c r="C1913">
-        <v>0.3960781983119439</v>
+        <v>0.3962493551068799</v>
       </c>
       <c r="D1913">
         <v>13.09809470992264</v>
@@ -76272,10 +76260,10 @@
         <v>16.49156808445106</v>
       </c>
       <c r="F1913">
-        <v>99.03240151443281</v>
+        <v>98.93114419183792</v>
       </c>
       <c r="G1913">
-        <v>35.94045183738282</v>
+        <v>35.9428135260994</v>
       </c>
       <c r="H1913">
         <v>17.31382909974914</v>
@@ -76284,13 +76272,13 @@
         <v>3.011924202444217</v>
       </c>
       <c r="J1913">
-        <v>52.70862164950428</v>
+        <v>52.71191330667695</v>
       </c>
       <c r="K1913">
-        <v>68.42848140300056</v>
+        <v>68.43297494427736</v>
       </c>
       <c r="L1913">
-        <v>81.70106312390982</v>
+        <v>81.70589384665863</v>
       </c>
     </row>
     <row r="1914" spans="1:12">
@@ -76301,7 +76289,7 @@
         <v>1.91667835183734</v>
       </c>
       <c r="C1914">
-        <v>0.3830143611479488</v>
+        <v>0.3831798726826607</v>
       </c>
       <c r="D1914">
         <v>12.92164332141544</v>
@@ -76310,10 +76298,10 @@
         <v>16.26830197641734</v>
       </c>
       <c r="F1914">
-        <v>101.0111956947211</v>
+        <v>100.9079151211741</v>
       </c>
       <c r="G1914">
-        <v>35.88030049589858</v>
+        <v>35.88265823200084</v>
       </c>
       <c r="H1914">
         <v>17.41004784604861</v>
@@ -76322,13 +76310,13 @@
         <v>3.022809939168784</v>
       </c>
       <c r="J1914">
-        <v>52.69804707080251</v>
+        <v>52.70133806759198</v>
       </c>
       <c r="K1914">
-        <v>68.43761439477134</v>
+        <v>68.44210853579075</v>
       </c>
       <c r="L1914">
-        <v>81.82438717320215</v>
+        <v>81.82922518770786</v>
       </c>
     </row>
     <row r="1915" spans="1:12">
@@ -76339,7 +76327,7 @@
         <v>1.926299579129382</v>
       </c>
       <c r="C1915">
-        <v>0.3924625962128141</v>
+        <v>0.3926321906019681</v>
       </c>
       <c r="D1915">
         <v>13.35167472748441</v>
@@ -76348,10 +76336,10 @@
         <v>16.77151621802827</v>
       </c>
       <c r="F1915">
-        <v>101.9303406100875</v>
+        <v>101.8261202415665</v>
       </c>
       <c r="G1915">
-        <v>36.93458259239681</v>
+        <v>36.9370096065967</v>
       </c>
       <c r="H1915">
         <v>17.74917387319721</v>
@@ -76360,13 +76348,13 @@
         <v>2.971854477051989</v>
       </c>
       <c r="J1915">
-        <v>54.42569118163421</v>
+        <v>54.42909006992134</v>
       </c>
       <c r="K1915">
-        <v>69.87171230961435</v>
+        <v>69.87630062455145</v>
       </c>
       <c r="L1915">
-        <v>83.76600023650781</v>
+        <v>83.77095305238862</v>
       </c>
     </row>
     <row r="1916" spans="1:12">
@@ -76377,7 +76365,7 @@
         <v>2.003145740387563</v>
       </c>
       <c r="C1916">
-        <v>0.4062606307361685</v>
+        <v>0.4064361876533676</v>
       </c>
       <c r="D1916">
         <v>13.83170551616947</v>
@@ -76386,10 +76374,10 @@
         <v>17.3745000625202</v>
       </c>
       <c r="F1916">
-        <v>100.7670421496841</v>
+        <v>100.6640112149815</v>
       </c>
       <c r="G1916">
-        <v>38.0279818144003</v>
+        <v>38.03048067712945</v>
       </c>
       <c r="H1916">
         <v>17.68096382202303</v>
@@ -76398,13 +76386,13 @@
         <v>3.013163417166612</v>
       </c>
       <c r="J1916">
-        <v>55.90404194673295</v>
+        <v>55.90753315813055</v>
       </c>
       <c r="K1916">
-        <v>72.42578179024591</v>
+        <v>72.4305378250622</v>
       </c>
       <c r="L1916">
-        <v>86.44128345882568</v>
+        <v>86.44639445565332</v>
       </c>
     </row>
     <row r="1917" spans="1:12">
@@ -76415,7 +76403,7 @@
         <v>1.98052921409964</v>
       </c>
       <c r="C1917">
-        <v>0.399589661855336</v>
+        <v>0.3997623360547847</v>
       </c>
       <c r="D1917">
         <v>13.86141963457136</v>
@@ -76424,10 +76412,10 @@
         <v>17.41182502952647</v>
       </c>
       <c r="F1917">
-        <v>102.2939826877222</v>
+        <v>102.1893905073235</v>
       </c>
       <c r="G1917">
-        <v>38.2581169060857</v>
+        <v>38.26063089125827</v>
       </c>
       <c r="H1917">
         <v>17.85155101637302</v>
@@ -76436,13 +76424,13 @@
         <v>3.00733758832779</v>
       </c>
       <c r="J1917">
-        <v>56.36028386619797</v>
+        <v>56.36380356993591</v>
       </c>
       <c r="K1917">
-        <v>72.79406694123827</v>
+        <v>72.79884716049493</v>
       </c>
       <c r="L1917">
-        <v>87.04537995700836</v>
+        <v>87.05052667213127</v>
       </c>
     </row>
     <row r="1918" spans="1:12">
@@ -76453,7 +76441,7 @@
         <v>2.011396140641815</v>
       </c>
       <c r="C1918">
-        <v>0.4116467401141758</v>
+        <v>0.4118246245243353</v>
       </c>
       <c r="D1918">
         <v>14.2947624440122</v>
@@ -76462,10 +76450,10 @@
         <v>17.95616243324872</v>
       </c>
       <c r="F1918">
-        <v>104.1285273602939</v>
+        <v>104.0220594192463</v>
       </c>
       <c r="G1918">
-        <v>39.32856138573175</v>
+        <v>39.33114571105087</v>
       </c>
       <c r="H1918">
         <v>17.97321515606089</v>
@@ -76474,13 +76462,13 @@
         <v>2.985948002282048</v>
       </c>
       <c r="J1918">
-        <v>57.95440032342992</v>
+        <v>57.95801957985405</v>
       </c>
       <c r="K1918">
-        <v>74.57193872744674</v>
+        <v>74.57683569546198</v>
       </c>
       <c r="L1918">
-        <v>89.10703298812133</v>
+        <v>89.112301602199</v>
       </c>
     </row>
     <row r="1919" spans="1:12">
@@ -76491,7 +76479,7 @@
         <v>2.0105036898435</v>
       </c>
       <c r="C1919">
-        <v>0.4118265173175172</v>
+        <v>0.4120044794145831</v>
       </c>
       <c r="D1919">
         <v>13.98799946078006</v>
@@ -76500,10 +76488,10 @@
         <v>17.5708264770201</v>
       </c>
       <c r="F1919">
-        <v>101.3595111662597</v>
+        <v>101.2558744517777</v>
       </c>
       <c r="G1919">
-        <v>38.33207570525972</v>
+        <v>38.33459455035064</v>
       </c>
       <c r="H1919">
         <v>18.08090149368568</v>
@@ -76512,13 +76500,13 @@
         <v>2.99377629951363</v>
       </c>
       <c r="J1919">
-        <v>56.64621242858306</v>
+        <v>56.64974998858006</v>
       </c>
       <c r="K1919">
-        <v>72.7802286284263</v>
+        <v>72.78500793895273</v>
       </c>
       <c r="L1919">
-        <v>87.31365887325533</v>
+        <v>87.31882145085314</v>
       </c>
     </row>
     <row r="1920" spans="1:12">
@@ -76529,7 +76517,7 @@
         <v>1.990657788718039</v>
       </c>
       <c r="C1920">
-        <v>0.406614656169607</v>
+        <v>0.4067903660713902</v>
       </c>
       <c r="D1920">
         <v>13.92511786628941</v>
@@ -76538,10 +76526,10 @@
         <v>17.4918386568896</v>
       </c>
       <c r="F1920">
-        <v>101.4655691938242</v>
+        <v>101.3618240385517</v>
       </c>
       <c r="G1920">
-        <v>38.19512771285343</v>
+        <v>38.19763755893316</v>
       </c>
       <c r="H1920">
         <v>17.9240375442338</v>
@@ -76550,13 +76538,13 @@
         <v>2.995688724043879</v>
       </c>
       <c r="J1920">
-        <v>56.33109195276288</v>
+        <v>56.33460983346374</v>
       </c>
       <c r="K1920">
-        <v>72.5434546395696</v>
+        <v>72.54821840169177</v>
       </c>
       <c r="L1920">
-        <v>86.86863304162533</v>
+        <v>86.873769306268</v>
       </c>
     </row>
     <row r="1921" spans="1:12">
@@ -76567,7 +76555,7 @@
         <v>1.964381012916838</v>
       </c>
       <c r="C1921">
-        <v>0.4081415267146746</v>
+        <v>0.408317896421188</v>
       </c>
       <c r="D1921">
         <v>13.66327327343902</v>
@@ -76576,10 +76564,10 @@
         <v>17.16292629756187</v>
       </c>
       <c r="F1921">
-        <v>99.79643980448098</v>
+        <v>99.69440127825558</v>
       </c>
       <c r="G1921">
-        <v>37.5068804452927</v>
+        <v>37.50934506584734</v>
       </c>
       <c r="H1921">
         <v>17.7946133106952</v>
@@ -76588,13 +76576,13 @@
         <v>2.942093009007046</v>
       </c>
       <c r="J1921">
-        <v>55.26511294281917</v>
+        <v>55.26856425305501</v>
       </c>
       <c r="K1921">
-        <v>70.58734090658683</v>
+        <v>70.59197621521096</v>
       </c>
       <c r="L1921">
-        <v>84.60367048801741</v>
+        <v>84.60867283266303</v>
       </c>
     </row>
     <row r="1922" spans="1:12">
@@ -76605,7 +76593,7 @@
         <v>1.990205557117942</v>
       </c>
       <c r="C1922">
-        <v>0.4139768094648916</v>
+        <v>0.414155700765114</v>
       </c>
       <c r="D1922">
         <v>13.67049836091531</v>
@@ -76614,10 +76602,10 @@
         <v>17.17200198838408</v>
       </c>
       <c r="F1922">
-        <v>98.12412272641444</v>
+        <v>98.02379408854139</v>
       </c>
       <c r="G1922">
-        <v>37.31059832003056</v>
+        <v>37.31305004265941</v>
       </c>
       <c r="H1922">
         <v>17.8470753093374</v>
@@ -76626,13 +76614,13 @@
         <v>2.931552076455686</v>
       </c>
       <c r="J1922">
-        <v>55.03109174666046</v>
+        <v>55.03452844225595</v>
       </c>
       <c r="K1922">
-        <v>70.09149094600815</v>
+        <v>70.09609369330373</v>
       </c>
       <c r="L1922">
-        <v>84.13114898558473</v>
+        <v>84.13612339154407</v>
       </c>
     </row>
     <row r="1923" spans="1:12">
@@ -76643,7 +76631,7 @@
         <v>1.99052635890926</v>
       </c>
       <c r="C1923">
-        <v>0.4156809393303352</v>
+        <v>0.4158605670341444</v>
       </c>
       <c r="D1923">
         <v>13.66738709802327</v>
@@ -76652,10 +76640,10 @@
         <v>17.16809381977471</v>
       </c>
       <c r="F1923">
-        <v>97.42094901831886</v>
+        <v>97.32133935207442</v>
       </c>
       <c r="G1923">
-        <v>37.21352690318972</v>
+        <v>37.21597224714335</v>
       </c>
       <c r="H1923">
         <v>18.01785029946934</v>
@@ -76664,13 +76652,13 @@
         <v>2.924105477191478</v>
       </c>
       <c r="J1923">
-        <v>55.02672076528381</v>
+        <v>55.0301571879112</v>
       </c>
       <c r="K1923">
-        <v>69.82011144355504</v>
+        <v>69.82469636998172</v>
       </c>
       <c r="L1923">
-        <v>84.03924310410987</v>
+        <v>84.04421207596818</v>
       </c>
     </row>
     <row r="1924" spans="1:12">
@@ -76681,7 +76669,7 @@
         <v>1.980903011781593</v>
       </c>
       <c r="C1924">
-        <v>0.4088517137277515</v>
+        <v>0.4090283903265239</v>
       </c>
       <c r="D1924">
         <v>13.39412502403688</v>
@@ -76690,10 +76678,10 @@
         <v>16.82483955398581</v>
       </c>
       <c r="F1924">
-        <v>96.47249620319585</v>
+        <v>96.37385629827394</v>
       </c>
       <c r="G1924">
-        <v>36.51121217604246</v>
+        <v>36.51361137008194</v>
       </c>
       <c r="H1924">
         <v>17.83292658121322</v>
@@ -76702,13 +76690,13 @@
         <v>2.942099979351542</v>
       </c>
       <c r="J1924">
-        <v>53.89896035119201</v>
+        <v>53.90232634510129</v>
       </c>
       <c r="K1924">
-        <v>68.71725800585129</v>
+        <v>68.72177051042463</v>
       </c>
       <c r="L1924">
-        <v>82.62890344545393</v>
+        <v>82.63378902843561</v>
       </c>
     </row>
     <row r="1925" spans="1:12">
@@ -76719,7 +76707,7 @@
         <v>1.971894416985307</v>
       </c>
       <c r="C1925">
-        <v>0.4061942037146901</v>
+        <v>0.4063697319268603</v>
       </c>
       <c r="D1925">
         <v>13.32880125423508</v>
@@ -76728,10 +76716,10 @@
         <v>16.74278403008974</v>
       </c>
       <c r="F1925">
-        <v>96.36432002965191</v>
+        <v>96.26579073125406</v>
       </c>
       <c r="G1925">
-        <v>36.39063012401218</v>
+        <v>36.39302139446536</v>
       </c>
       <c r="H1925">
         <v>17.78246162069193</v>
@@ -76740,13 +76728,13 @@
         <v>2.979300873486233</v>
       </c>
       <c r="J1925">
-        <v>53.69172197227865</v>
+        <v>53.69507502413642</v>
       </c>
       <c r="K1925">
-        <v>68.92475413175526</v>
+        <v>68.92928026212283</v>
       </c>
       <c r="L1925">
-        <v>82.79499897059155</v>
+        <v>82.79989437427079</v>
       </c>
     </row>
     <row r="1926" spans="1:12">
@@ -76757,7 +76745,7 @@
         <v>1.974159108045163</v>
       </c>
       <c r="C1926">
-        <v>0.4026202189658396</v>
+        <v>0.4027942027562834</v>
       </c>
       <c r="D1926">
         <v>13.19479013363919</v>
@@ -76766,10 +76754,10 @@
         <v>16.57444786789702</v>
       </c>
       <c r="F1926">
-        <v>96.05397105690383</v>
+        <v>95.95575907996411</v>
       </c>
       <c r="G1926">
-        <v>36.04980497175295</v>
+        <v>36.05217384619063</v>
       </c>
       <c r="H1926">
         <v>17.63986250348309</v>
@@ -76778,13 +76766,13 @@
         <v>2.990491840272386</v>
       </c>
       <c r="J1926">
-        <v>53.1063627834053</v>
+        <v>53.10967927954007</v>
       </c>
       <c r="K1926">
-        <v>68.40867179018589</v>
+        <v>68.4131640306109</v>
       </c>
       <c r="L1926">
-        <v>82.07107017040599</v>
+        <v>82.07592277048893</v>
       </c>
     </row>
     <row r="1927" spans="1:12">
@@ -76795,7 +76783,7 @@
         <v>2.001390516489692</v>
       </c>
       <c r="C1927">
-        <v>0.4053500209024105</v>
+        <v>0.4055251843188784</v>
       </c>
       <c r="D1927">
         <v>13.29640388440565</v>
@@ -76804,10 +76792,10 @@
         <v>16.70208853498474</v>
       </c>
       <c r="F1927">
-        <v>96.21817644782023</v>
+        <v>96.1197965763532</v>
       </c>
       <c r="G1927">
-        <v>36.21419735386245</v>
+        <v>36.21657703071396</v>
       </c>
       <c r="H1927">
         <v>17.94096371012829</v>
@@ -76816,13 +76804,13 @@
         <v>3.010838304458429</v>
       </c>
       <c r="J1927">
-        <v>53.5630498629564</v>
+        <v>53.56639487923179</v>
       </c>
       <c r="K1927">
-        <v>68.9533420042269</v>
+        <v>68.95787001189443</v>
       </c>
       <c r="L1927">
-        <v>83.00940065458195</v>
+        <v>83.01430873514755</v>
       </c>
     </row>
     <row r="1928" spans="1:12">
@@ -76833,7 +76821,7 @@
         <v>2.094209639185638</v>
       </c>
       <c r="C1928">
-        <v>0.4154335090523363</v>
+        <v>0.4156130298343972</v>
       </c>
       <c r="D1928">
         <v>13.53936571493157</v>
@@ -76842,10 +76830,10 @@
         <v>17.00728158111544</v>
       </c>
       <c r="F1928">
-        <v>96.56047992608227</v>
+        <v>96.46175006074259</v>
       </c>
       <c r="G1928">
-        <v>36.76075145788574</v>
+        <v>36.76316704944045</v>
       </c>
       <c r="H1928">
         <v>18.08791180223919</v>
@@ -76854,13 +76842,13 @@
         <v>3.074311681180818</v>
       </c>
       <c r="J1928">
-        <v>54.44069699695056</v>
+        <v>54.44409682235192</v>
       </c>
       <c r="K1928">
-        <v>70.7208282054532</v>
+        <v>70.7254722798818</v>
       </c>
       <c r="L1928">
-        <v>85.0943834081119</v>
+        <v>85.09941476704417</v>
       </c>
     </row>
     <row r="1929" spans="1:12">
@@ -76871,7 +76859,7 @@
         <v>2.133997540651581</v>
       </c>
       <c r="C1929">
-        <v>0.4179058959298473</v>
+        <v>0.4180864851014727</v>
       </c>
       <c r="D1929">
         <v>13.52580612066244</v>
@@ -76880,10 +76868,10 @@
         <v>16.99024888972382</v>
       </c>
       <c r="F1929">
-        <v>95.77108770583473</v>
+        <v>95.67316496767239</v>
       </c>
       <c r="G1929">
-        <v>36.46936933473953</v>
+        <v>36.47176577923744</v>
       </c>
       <c r="H1929">
         <v>18.16007339034071</v>
@@ -76892,13 +76880,13 @@
         <v>3.132223900424842</v>
       </c>
       <c r="J1929">
-        <v>54.08504948546321</v>
+        <v>54.08842710065217</v>
       </c>
       <c r="K1929">
-        <v>70.82636369625605</v>
+        <v>70.83101470095804</v>
       </c>
       <c r="L1929">
-        <v>85.29354067157065</v>
+        <v>85.29858380603541</v>
       </c>
     </row>
     <row r="1930" spans="1:12">
@@ -76909,7 +76897,7 @@
         <v>2.111926518731272</v>
       </c>
       <c r="C1930">
-        <v>0.4162475305295418</v>
+        <v>0.4164274030737234</v>
       </c>
       <c r="D1930">
         <v>13.45068012483678</v>
@@ -76918,10 +76906,10 @@
         <v>16.89588043909104</v>
       </c>
       <c r="F1930">
-        <v>95.61223713338465</v>
+        <v>95.51447681462669</v>
       </c>
       <c r="G1930">
-        <v>36.26380634466376</v>
+        <v>36.26618928137952</v>
       </c>
       <c r="H1930">
         <v>18.20867910462738</v>
@@ -76930,13 +76918,13 @@
         <v>3.131100507174105</v>
       </c>
       <c r="J1930">
-        <v>53.8316267128934</v>
+        <v>53.83498850181218</v>
       </c>
       <c r="K1930">
-        <v>70.41444313720545</v>
+        <v>70.41906709203001</v>
       </c>
       <c r="L1930">
-        <v>84.90415856829901</v>
+        <v>84.90917867984446</v>
       </c>
     </row>
     <row r="1931" spans="1:12">
@@ -76947,7 +76935,7 @@
         <v>2.14625160379043</v>
       </c>
       <c r="C1931">
-        <v>0.4281416027233996</v>
+        <v>0.4283266150386773</v>
       </c>
       <c r="D1931">
         <v>13.7617586348014</v>
@@ -76956,10 +76944,10 @@
         <v>17.28663728281581</v>
       </c>
       <c r="F1931">
-        <v>94.36351299255686</v>
+        <v>94.267029452522</v>
       </c>
       <c r="G1931">
-        <v>36.79299871378431</v>
+        <v>36.79541642434356</v>
       </c>
       <c r="H1931">
         <v>18.22278516228723</v>
@@ -76968,13 +76956,13 @@
         <v>3.05947516602447</v>
       </c>
       <c r="J1931">
-        <v>54.58833152872665</v>
+        <v>54.59174057391503</v>
       </c>
       <c r="K1931">
-        <v>70.63660957714845</v>
+        <v>70.64124812113306</v>
       </c>
       <c r="L1931">
-        <v>85.16169712700359</v>
+        <v>85.16673246598093</v>
       </c>
     </row>
     <row r="1932" spans="1:12">
@@ -76985,7 +76973,7 @@
         <v>2.152829453736202</v>
       </c>
       <c r="C1932">
-        <v>0.4368752693318628</v>
+        <v>0.4370640557159762</v>
       </c>
       <c r="D1932">
         <v>14.00136499894038</v>
@@ -76994,10 +76982,10 @@
         <v>17.58761540759198</v>
       </c>
       <c r="F1932">
-        <v>94.65811764431378</v>
+        <v>94.56133288086309</v>
       </c>
       <c r="G1932">
-        <v>37.09549638074483</v>
+        <v>37.09793396877613</v>
       </c>
       <c r="H1932">
         <v>18.35730408224619</v>
@@ -77006,13 +76994,13 @@
         <v>3.021750943350948</v>
       </c>
       <c r="J1932">
-        <v>55.11543678303203</v>
+        <v>55.11887874598104</v>
       </c>
       <c r="K1932">
-        <v>70.78187117909128</v>
+        <v>70.78651926207181</v>
       </c>
       <c r="L1932">
-        <v>85.47647979763005</v>
+        <v>85.48153374870067</v>
       </c>
     </row>
     <row r="1933" spans="1:12">
@@ -77023,7 +77011,7 @@
         <v>2.140687035273625</v>
       </c>
       <c r="C1933">
-        <v>0.4380811688552448</v>
+        <v>0.4382704763432672</v>
       </c>
       <c r="D1933">
         <v>14.04456847108128</v>
@@ -77032,10 +77020,10 @@
         <v>17.64188483434747</v>
       </c>
       <c r="F1933">
-        <v>94.86570104639029</v>
+        <v>94.76870403584483</v>
       </c>
       <c r="G1933">
-        <v>37.18999742413391</v>
+        <v>37.19244122193822</v>
       </c>
       <c r="H1933">
         <v>18.38541528991622</v>
@@ -77044,13 +77032,13 @@
         <v>2.996824379163017</v>
       </c>
       <c r="J1933">
-        <v>55.26992347386705</v>
+        <v>55.27337508452089</v>
       </c>
       <c r="K1933">
-        <v>70.67024702910689</v>
+        <v>70.67488778198576</v>
       </c>
       <c r="L1933">
-        <v>85.38788510268364</v>
+        <v>85.3929338154331</v>
       </c>
     </row>
     <row r="1934" spans="1:12">
@@ -77061,7 +77049,7 @@
         <v>2.141362556226268</v>
       </c>
       <c r="C1934">
-        <v>0.4455425504926737</v>
+        <v>0.4457350822585591</v>
       </c>
       <c r="D1934">
         <v>14.22991626102639</v>
@@ -77070,10 +77058,10 @@
         <v>17.87470682323559</v>
       </c>
       <c r="F1934">
-        <v>95.57047951889251</v>
+        <v>95.47276189590045</v>
       </c>
       <c r="G1934">
-        <v>37.52562797777135</v>
+        <v>37.52809383024807</v>
       </c>
       <c r="H1934">
         <v>18.42020132880202</v>
@@ -77082,13 +77070,13 @@
         <v>2.938143137598954</v>
       </c>
       <c r="J1934">
-        <v>55.76992432921386</v>
+        <v>55.77340716495671</v>
       </c>
       <c r="K1934">
-        <v>70.61612653160766</v>
+        <v>70.62076373051771</v>
       </c>
       <c r="L1934">
-        <v>85.36942217233576</v>
+        <v>85.37446979343115</v>
       </c>
     </row>
     <row r="1935" spans="1:12">
@@ -77099,7 +77087,7 @@
         <v>2.079577827086907</v>
       </c>
       <c r="C1935">
-        <v>0.4371935604358835</v>
+        <v>0.4373824843627485</v>
       </c>
       <c r="D1935">
         <v>13.98961503680163</v>
@@ -77108,10 +77096,10 @@
         <v>17.57285585985034</v>
       </c>
       <c r="F1935">
-        <v>94.60544653390501</v>
+        <v>94.50871562490535</v>
       </c>
       <c r="G1935">
-        <v>36.97685702612621</v>
+        <v>36.97928681822812</v>
       </c>
       <c r="H1935">
         <v>18.41707065212859</v>
@@ -77120,13 +77108,13 @@
         <v>2.913554328096047</v>
       </c>
       <c r="J1935">
-        <v>54.99275968626935</v>
+        <v>54.99619398802494</v>
       </c>
       <c r="K1935">
-        <v>69.28795646038553</v>
+        <v>69.29250644141619</v>
       </c>
       <c r="L1935">
-        <v>83.92070566976732</v>
+        <v>83.92566763288595</v>
       </c>
     </row>
     <row r="1936" spans="1:12">
@@ -77137,7 +77125,7 @@
         <v>2.146687583317398</v>
       </c>
       <c r="C1936">
-        <v>0.4487781299632153</v>
+        <v>0.4489720599161613</v>
       </c>
       <c r="D1936">
         <v>14.50513420246357</v>
@@ -77146,10 +77134,10 @@
         <v>18.2204179240913</v>
       </c>
       <c r="F1936">
-        <v>96.81221684708107</v>
+        <v>96.71322958914837</v>
       </c>
       <c r="G1936">
-        <v>38.17365646010052</v>
+        <v>38.17616489527937</v>
       </c>
       <c r="H1936">
         <v>18.50293209480699</v>
@@ -77158,13 +77146,13 @@
         <v>2.963166886699745</v>
       </c>
       <c r="J1936">
-        <v>56.7477645700257</v>
+        <v>56.75130847196116</v>
       </c>
       <c r="K1936">
-        <v>72.12046686713681</v>
+        <v>72.12520285262305</v>
       </c>
       <c r="L1936">
-        <v>87.10614749708617</v>
+        <v>87.11129780519948</v>
       </c>
     </row>
     <row r="1937" spans="1:12">
@@ -77175,7 +77163,7 @@
         <v>2.034837282988039</v>
       </c>
       <c r="C1937">
-        <v>0.4133210674783617</v>
+        <v>0.4134996754135886</v>
       </c>
       <c r="D1937">
         <v>13.30531244448908</v>
@@ -77184,10 +77172,10 @@
         <v>16.71327889596702</v>
       </c>
       <c r="F1937">
-        <v>90.50767213878116</v>
+        <v>90.41513106722361</v>
       </c>
       <c r="G1937">
-        <v>35.23994155884581</v>
+        <v>35.24225721622066</v>
       </c>
       <c r="H1937">
         <v>18.41326428385642</v>
@@ -77196,13 +77184,13 @@
         <v>3.004662362096937</v>
       </c>
       <c r="J1937">
-        <v>52.53590222361056</v>
+        <v>52.53918309444278</v>
       </c>
       <c r="K1937">
-        <v>67.08285669232883</v>
+        <v>67.08726186952015</v>
       </c>
       <c r="L1937">
-        <v>81.52469219642896</v>
+        <v>81.52951249092848</v>
       </c>
     </row>
     <row r="1938" spans="1:12">
@@ -77213,7 +77201,7 @@
         <v>1.995729848757866</v>
       </c>
       <c r="C1938">
-        <v>0.4045912817079937</v>
+        <v>0.4047661172514067</v>
       </c>
       <c r="D1938">
         <v>12.86851750627</v>
@@ -77222,10 +77210,10 @@
         <v>16.16460514980288</v>
       </c>
       <c r="F1938">
-        <v>88.98048037002316</v>
+        <v>88.88950080103677</v>
       </c>
       <c r="G1938">
-        <v>34.24593397582113</v>
+        <v>34.24818431580644</v>
       </c>
       <c r="H1938">
         <v>18.53949731808645</v>
@@ -77234,13 +77222,13 @@
         <v>2.994596852055555</v>
       </c>
       <c r="J1938">
-        <v>51.21816436789648</v>
+        <v>51.22136294590584</v>
       </c>
       <c r="K1938">
-        <v>65.07829835582625</v>
+        <v>65.08257189827364</v>
       </c>
       <c r="L1938">
-        <v>79.47192023202921</v>
+        <v>79.47661915268306</v>
       </c>
     </row>
     <row r="1939" spans="1:12">
@@ -77251,7 +77239,7 @@
         <v>1.926424649431284</v>
       </c>
       <c r="C1939">
-        <v>0.3869988568898233</v>
+        <v>0.3871660902398819</v>
       </c>
       <c r="D1939">
         <v>12.17141731345251</v>
@@ -77260,10 +77248,10 @@
         <v>15.29182636973404</v>
       </c>
       <c r="F1939">
-        <v>88.09450375827518</v>
+        <v>88.00443007078027</v>
       </c>
       <c r="G1939">
-        <v>32.93800827815222</v>
+        <v>32.94017267282508</v>
       </c>
       <c r="H1939">
         <v>17.94544019893926</v>
@@ -77272,13 +77260,13 @@
         <v>3.013365900369302</v>
       </c>
       <c r="J1939">
-        <v>48.94954620293121</v>
+        <v>48.95260310557473</v>
       </c>
       <c r="K1939">
-        <v>62.79676210776366</v>
+        <v>62.80088582696356</v>
       </c>
       <c r="L1939">
-        <v>76.32775753438544</v>
+        <v>76.33227055074761</v>
       </c>
     </row>
     <row r="1940" spans="1:12">
@@ -77289,7 +77277,7 @@
         <v>1.965571653926466</v>
       </c>
       <c r="C1940">
-        <v>0.3957879357147963</v>
+        <v>0.3959589670789052</v>
       </c>
       <c r="D1940">
         <v>12.40474845226979</v>
@@ -77298,10 +77286,10 @@
         <v>15.50606324587384</v>
       </c>
       <c r="F1940">
-        <v>88.00272895718965</v>
+        <v>87.91274910636332</v>
       </c>
       <c r="G1940">
-        <v>33.28548754490402</v>
+        <v>33.28767477284195</v>
       </c>
       <c r="H1940">
         <v>17.98726167188071</v>
@@ -77310,13 +77298,13 @@
         <v>2.987814114772148</v>
       </c>
       <c r="J1940">
-        <v>49.46863839686986</v>
+        <v>49.47172771685783</v>
       </c>
       <c r="K1940">
-        <v>63.19299402460359</v>
+        <v>63.1971437634438</v>
       </c>
       <c r="L1940">
-        <v>76.8056758077492</v>
+        <v>76.81021708189147</v>
       </c>
     </row>
     <row r="1941" spans="1:12">
@@ -77327,7 +77315,7 @@
         <v>1.949584560251199</v>
       </c>
       <c r="C1941">
-        <v>0.3907029877327444</v>
+        <v>0.3908718217444044</v>
       </c>
       <c r="D1941">
         <v>12.19562666246058</v>
@@ -77336,10 +77324,10 @@
         <v>15.26015956817815</v>
       </c>
       <c r="F1941">
-        <v>87.64118391273769</v>
+        <v>87.55157372964273</v>
       </c>
       <c r="G1941">
-        <v>32.88872879769144</v>
+        <v>32.89088995415258</v>
       </c>
       <c r="H1941">
         <v>18.04269324703514</v>
@@ -77348,13 +77336,13 @@
         <v>3.012605638386853</v>
       </c>
       <c r="J1941">
-        <v>48.9465735908525</v>
+        <v>48.94963030785619</v>
       </c>
       <c r="K1941">
-        <v>62.70191500385889</v>
+        <v>62.70603249466722</v>
       </c>
       <c r="L1941">
-        <v>76.32767099872838</v>
+        <v>76.33218400997397</v>
       </c>
     </row>
     <row r="1942" spans="1:12">
@@ -77365,7 +77353,7 @@
         <v>1.94395498344188</v>
       </c>
       <c r="C1942">
-        <v>0.3890804391355974</v>
+        <v>0.3892485719972857</v>
       </c>
       <c r="D1942">
         <v>12.12367816071924</v>
@@ -77374,10 +77362,10 @@
         <v>15.18225225644753</v>
       </c>
       <c r="F1942">
-        <v>87.5570543675591</v>
+        <v>87.46753020411393</v>
       </c>
       <c r="G1942">
-        <v>32.77614765076303</v>
+        <v>32.77830140938661</v>
       </c>
       <c r="H1942">
         <v>18.09049306511518</v>
@@ -77386,13 +77374,13 @@
         <v>3.00849664357201</v>
       </c>
       <c r="J1942">
-        <v>48.81982046604476</v>
+        <v>48.82286926730679</v>
       </c>
       <c r="K1942">
-        <v>62.44451994322622</v>
+        <v>62.44862053149184</v>
       </c>
       <c r="L1942">
-        <v>76.09622736094487</v>
+        <v>76.10072668766784</v>
       </c>
     </row>
     <row r="1943" spans="1:12">
@@ -77403,7 +77391,7 @@
         <v>1.999767429012472</v>
       </c>
       <c r="C1943">
-        <v>0.3965877212246373</v>
+        <v>0.3967590981990957</v>
       </c>
       <c r="D1943">
         <v>12.34283793189502</v>
@@ -77412,10 +77400,10 @@
         <v>15.40422211229568</v>
       </c>
       <c r="F1943">
-        <v>87.71767931294296</v>
+        <v>87.62799091585644</v>
       </c>
       <c r="G1943">
-        <v>32.993719064588</v>
+        <v>32.99588712008117</v>
       </c>
       <c r="H1943">
         <v>18.27872883111298</v>
@@ -77424,13 +77412,13 @@
         <v>3.042638576950357</v>
       </c>
       <c r="J1943">
-        <v>49.25468325202446</v>
+        <v>49.25775921049841</v>
       </c>
       <c r="K1943">
-        <v>63.21335895377317</v>
+        <v>63.21751002993153</v>
       </c>
       <c r="L1943">
-        <v>77.13740836771306</v>
+        <v>77.14196925614139</v>
       </c>
     </row>
     <row r="1944" spans="1:12">
@@ -77441,7 +77429,7 @@
         <v>2.007858134982939</v>
       </c>
       <c r="C1944">
-        <v>0.3894136572295696</v>
+        <v>0.3895819340843918</v>
       </c>
       <c r="D1944">
         <v>12.12149900651383</v>
@@ -77450,10 +77438,10 @@
         <v>15.20150617769988</v>
       </c>
       <c r="F1944">
-        <v>87.78843976517086</v>
+        <v>87.69867901788552</v>
       </c>
       <c r="G1944">
-        <v>32.44752948456283</v>
+        <v>32.4496616493061</v>
       </c>
       <c r="H1944">
         <v>18.67127653945144</v>
@@ -77462,13 +77450,13 @@
         <v>3.113892409931867</v>
       </c>
       <c r="J1944">
-        <v>48.74451710908298</v>
+        <v>48.747561207645</v>
       </c>
       <c r="K1944">
-        <v>62.90708183288131</v>
+        <v>62.91121279652429</v>
       </c>
       <c r="L1944">
-        <v>77.21518560526178</v>
+        <v>77.2197510924096</v>
       </c>
     </row>
     <row r="1945" spans="1:12">
@@ -77479,7 +77467,7 @@
         <v>2.082580927556295</v>
       </c>
       <c r="C1945">
-        <v>0.3984852623233227</v>
+        <v>0.3986574592799314</v>
       </c>
       <c r="D1945">
         <v>12.42933490460468</v>
@@ -77488,10 +77476,10 @@
         <v>15.57447026245975</v>
       </c>
       <c r="F1945">
-        <v>87.79744640548539</v>
+        <v>87.70767644921118</v>
       </c>
       <c r="G1945">
-        <v>33.05646741500348</v>
+        <v>33.05863959376344</v>
       </c>
       <c r="H1945">
         <v>18.61891818782566</v>
@@ -77500,13 +77488,13 @@
         <v>3.186161161771746</v>
       </c>
       <c r="J1945">
-        <v>49.57938653734717</v>
+        <v>49.58248277356439</v>
       </c>
       <c r="K1945">
-        <v>64.81763892508691</v>
+        <v>64.82189535062791</v>
       </c>
       <c r="L1945">
-        <v>79.27165244071092</v>
+        <v>79.27633952017032</v>
       </c>
     </row>
     <row r="1946" spans="1:12">
@@ -77517,7 +77505,7 @@
         <v>2.071199530083255</v>
       </c>
       <c r="C1946">
-        <v>0.4000012537353003</v>
+        <v>0.4001741057954525</v>
       </c>
       <c r="D1946">
         <v>12.54385255273632</v>
@@ -77526,10 +77514,10 @@
         <v>15.75405205484378</v>
       </c>
       <c r="F1946">
-        <v>88.45298321414263</v>
+        <v>88.3625429933783</v>
       </c>
       <c r="G1946">
-        <v>33.49068079609378</v>
+        <v>33.49288150751791</v>
       </c>
       <c r="H1946">
         <v>18.57103777299976</v>
@@ -77538,13 +77526,13 @@
         <v>3.15608794812394</v>
       </c>
       <c r="J1946">
-        <v>50.16619969532108</v>
+        <v>50.16933257806177</v>
       </c>
       <c r="K1946">
-        <v>65.36315425571669</v>
+        <v>65.36744650399707</v>
       </c>
       <c r="L1946">
-        <v>79.8211349910717</v>
+        <v>79.82585455967818</v>
       </c>
     </row>
     <row r="1947" spans="1:12">
@@ -77555,7 +77543,7 @@
         <v>2.065458308597661</v>
       </c>
       <c r="C1947">
-        <v>0.4049582820580639</v>
+        <v>0.4051332761928966</v>
       </c>
       <c r="D1947">
         <v>12.71202996538781</v>
@@ -77564,10 +77552,10 @@
         <v>15.94893933343094</v>
       </c>
       <c r="F1947">
-        <v>87.8978986276517</v>
+        <v>87.80802596233571</v>
       </c>
       <c r="G1947">
-        <v>33.74254727904929</v>
+        <v>33.74476454091172</v>
       </c>
       <c r="H1947">
         <v>18.63273568786731</v>
@@ -77576,13 +77564,13 @@
         <v>3.140069491149315</v>
       </c>
       <c r="J1947">
-        <v>50.56627695239091</v>
+        <v>50.56943481998479</v>
       </c>
       <c r="K1947">
-        <v>65.68884492644806</v>
+        <v>65.69315856208706</v>
       </c>
       <c r="L1947">
-        <v>80.24539027570114</v>
+        <v>80.25013492916669</v>
       </c>
     </row>
     <row r="1948" spans="1:12">
@@ -77593,7 +77581,7 @@
         <v>2.065653333475203</v>
       </c>
       <c r="C1948">
-        <v>0.3982913973656829</v>
+        <v>0.3984635105476608</v>
       </c>
       <c r="D1948">
         <v>12.52239300853714</v>
@@ -77602,10 +77590,10 @@
         <v>15.71048281298544</v>
       </c>
       <c r="F1948">
-        <v>88.63742592935394</v>
+        <v>88.5467971220742</v>
       </c>
       <c r="G1948">
-        <v>33.46940976100545</v>
+        <v>33.47160907468523</v>
       </c>
       <c r="H1948">
         <v>18.47911025253108</v>
@@ -77614,13 +77602,13 @@
         <v>3.177063212471553</v>
       </c>
       <c r="J1948">
-        <v>50.07319286216418</v>
+        <v>50.07631993662152</v>
       </c>
       <c r="K1948">
-        <v>65.54405611004798</v>
+        <v>65.54836023773781</v>
       </c>
       <c r="L1948">
-        <v>79.92079963554589</v>
+        <v>79.92552509700427</v>
       </c>
     </row>
     <row r="1949" spans="1:12">
@@ -77631,7 +77619,7 @@
         <v>1.98333658307961</v>
       </c>
       <c r="C1949">
-        <v>0.3885321728542295</v>
+        <v>0.3887000687942699</v>
       </c>
       <c r="D1949">
         <v>11.96151583597917</v>
@@ -77640,10 +77628,10 @@
         <v>14.99552220810253</v>
       </c>
       <c r="F1949">
-        <v>86.63172779840832</v>
+        <v>86.54314975047166</v>
       </c>
       <c r="G1949">
-        <v>32.01733730622247</v>
+        <v>32.01944120253941</v>
       </c>
       <c r="H1949">
         <v>18.798163928695</v>
@@ -77652,13 +77640,13 @@
         <v>3.106184729342201</v>
       </c>
       <c r="J1949">
-        <v>48.2255220991447</v>
+        <v>48.22853378643138</v>
       </c>
       <c r="K1949">
-        <v>61.96929769108747</v>
+        <v>61.97336707259874</v>
       </c>
       <c r="L1949">
-        <v>76.34279401942328</v>
+        <v>76.3473079248447</v>
       </c>
     </row>
     <row r="1950" spans="1:12">
@@ -77669,7 +77657,7 @@
         <v>2.02584635348863</v>
       </c>
       <c r="C1950">
-        <v>0.3913423627012622</v>
+        <v>0.3915114730052577</v>
       </c>
       <c r="D1950">
         <v>11.95451835457737</v>
@@ -77678,10 +77666,10 @@
         <v>14.97477939166844</v>
       </c>
       <c r="F1950">
-        <v>85.8443102435283</v>
+        <v>85.75653730373952</v>
       </c>
       <c r="G1950">
-        <v>32.04055669579865</v>
+        <v>32.04266211788858</v>
       </c>
       <c r="H1950">
         <v>18.74452147151115</v>
@@ -77690,13 +77678,13 @@
         <v>3.127422107586832</v>
       </c>
       <c r="J1950">
-        <v>48.224343088296</v>
+        <v>48.22735470195337</v>
       </c>
       <c r="K1950">
-        <v>62.22608459890953</v>
+        <v>62.23017084302751</v>
       </c>
       <c r="L1950">
-        <v>76.57304376859975</v>
+        <v>76.57757128795296</v>
       </c>
     </row>
     <row r="1951" spans="1:12">
@@ -77707,7 +77695,7 @@
         <v>2.051022934600222</v>
       </c>
       <c r="C1951">
-        <v>0.3963594712537336</v>
+        <v>0.3965307495948071</v>
       </c>
       <c r="D1951">
         <v>12.11019900075616</v>
@@ -77716,10 +77704,10 @@
         <v>15.15817927702188</v>
       </c>
       <c r="F1951">
-        <v>85.64976331061062</v>
+        <v>85.56218928856235</v>
       </c>
       <c r="G1951">
-        <v>32.28496801159669</v>
+        <v>32.28708949423726</v>
       </c>
       <c r="H1951">
         <v>19.28414686627979</v>
@@ -77728,13 +77716,13 @@
         <v>3.127398033604274</v>
       </c>
       <c r="J1951">
-        <v>48.92088993335202</v>
+        <v>48.92394504640943</v>
       </c>
       <c r="K1951">
-        <v>62.70051722731297</v>
+        <v>62.70463462633246</v>
       </c>
       <c r="L1951">
-        <v>77.64958505758133</v>
+        <v>77.65417622938038</v>
       </c>
     </row>
     <row r="1952" spans="1:12">
@@ -77745,7 +77733,7 @@
         <v>2.037738631347403</v>
       </c>
       <c r="C1952">
-        <v>0.3909063449513563</v>
+        <v>0.3910752668395265</v>
       </c>
       <c r="D1952">
         <v>12.02743094413641</v>
@@ -77754,10 +77742,10 @@
         <v>15.06255074966544</v>
       </c>
       <c r="F1952">
-        <v>86.44484885552299</v>
+        <v>86.35646188506308</v>
       </c>
       <c r="G1952">
-        <v>32.29159202693117</v>
+        <v>32.29371394484345</v>
       </c>
       <c r="H1952">
         <v>19.27550986501657</v>
@@ -77766,13 +77754,13 @@
         <v>3.142377675728003</v>
       </c>
       <c r="J1952">
-        <v>48.92494765031702</v>
+        <v>48.92800301677914</v>
       </c>
       <c r="K1952">
-        <v>62.86354348273613</v>
+        <v>62.86767158731553</v>
       </c>
       <c r="L1952">
-        <v>77.82259611817888</v>
+        <v>77.82719751956901</v>
       </c>
     </row>
     <row r="1953" spans="1:12">
@@ -77783,7 +77771,7 @@
         <v>2.084901440954286</v>
       </c>
       <c r="C1953">
-        <v>0.3996924984066169</v>
+        <v>0.3998652170447008</v>
       </c>
       <c r="D1953">
         <v>12.2715168968241</v>
@@ -77792,10 +77780,10 @@
         <v>15.33640605059009</v>
       </c>
       <c r="F1953">
-        <v>85.91594166895909</v>
+        <v>85.82809548843056</v>
       </c>
       <c r="G1953">
-        <v>32.7324905458671</v>
+        <v>32.73464143573171</v>
       </c>
       <c r="H1953">
         <v>19.27550992176041</v>
@@ -77804,13 +77792,13 @@
         <v>3.133140681256923</v>
       </c>
       <c r="J1953">
-        <v>49.55955220173594</v>
+        <v>49.56264719929746</v>
       </c>
       <c r="K1953">
-        <v>63.62946768166975</v>
+        <v>63.63364608273291</v>
       </c>
       <c r="L1953">
-        <v>78.67596182523395</v>
+        <v>78.68061368341101</v>
       </c>
     </row>
     <row r="1954" spans="1:12">
@@ -77821,7 +77809,7 @@
         <v>2.038448069670054</v>
       </c>
       <c r="C1954">
-        <v>0.3860631753717018</v>
+        <v>0.3862300043868329</v>
       </c>
       <c r="D1954">
         <v>11.884293609699</v>
@@ -77830,10 +77818,10 @@
         <v>14.89087211284733</v>
       </c>
       <c r="F1954">
-        <v>86.25310345158644</v>
+        <v>86.1649125343973</v>
       </c>
       <c r="G1954">
-        <v>32.19212736618275</v>
+        <v>32.19424274815697</v>
       </c>
       <c r="H1954">
         <v>18.90643461289685</v>
@@ -77842,13 +77830,13 @@
         <v>3.153316055322736</v>
       </c>
       <c r="J1954">
-        <v>48.54507390470624</v>
+        <v>48.54810554802592</v>
       </c>
       <c r="K1954">
-        <v>62.78390888166167</v>
+        <v>62.78803175681966</v>
       </c>
       <c r="L1954">
-        <v>77.35839471303115</v>
+        <v>77.36296866767574</v>
       </c>
     </row>
     <row r="1955" spans="1:12">
@@ -77859,7 +77847,7 @@
         <v>2.008904627170034</v>
       </c>
       <c r="C1955">
-        <v>0.3836043003306916</v>
+        <v>0.3837700667951119</v>
       </c>
       <c r="D1955">
         <v>11.75876335734698</v>
@@ -77868,10 +77856,10 @@
         <v>14.75421092883292</v>
       </c>
       <c r="F1955">
-        <v>85.72421789955806</v>
+        <v>85.63656775017964</v>
       </c>
       <c r="G1955">
-        <v>32.02825243509196</v>
+        <v>32.03035704865466</v>
       </c>
       <c r="H1955">
         <v>18.71292195442601</v>
@@ -77880,13 +77868,13 @@
         <v>3.158408004403091</v>
       </c>
       <c r="J1955">
-        <v>48.1860917318404</v>
+        <v>48.18910095669784</v>
       </c>
       <c r="K1955">
-        <v>62.51499709743243</v>
+        <v>62.5191023137709</v>
       </c>
       <c r="L1955">
-        <v>76.86224588799261</v>
+        <v>76.86679050694286</v>
       </c>
     </row>
     <row r="1956" spans="1:12">
@@ -77897,7 +77885,7 @@
         <v>1.955109558502994</v>
       </c>
       <c r="C1956">
-        <v>0.3675350349792146</v>
+        <v>0.3676938574513468</v>
       </c>
       <c r="D1956">
         <v>11.47204288520807</v>
@@ -77906,10 +77894,10 @@
         <v>14.55512492168672</v>
       </c>
       <c r="F1956">
-        <v>88.83846288971102</v>
+        <v>88.74762852885449</v>
       </c>
       <c r="G1956">
-        <v>31.90398600686672</v>
+        <v>31.9060824547385</v>
       </c>
       <c r="H1956">
         <v>18.8797261737968</v>
@@ -77918,13 +77906,13 @@
         <v>3.163752458625928</v>
       </c>
       <c r="J1956">
-        <v>48.11586328301363</v>
+        <v>48.11886812209944</v>
       </c>
       <c r="K1956">
-        <v>62.32533705964318</v>
+        <v>62.32942982144239</v>
       </c>
       <c r="L1956">
-        <v>76.82366209136862</v>
+        <v>76.82820442898229</v>
       </c>
     </row>
     <row r="1957" spans="1:12">
@@ -77935,7 +77923,7 @@
         <v>1.952246367184886</v>
       </c>
       <c r="C1957">
-        <v>0.3671994831004606</v>
+        <v>0.3673581605709635</v>
       </c>
       <c r="D1957">
         <v>11.4931360632483</v>
@@ -77944,10 +77932,10 @@
         <v>14.5851395973216</v>
       </c>
       <c r="F1957">
-        <v>89.00692255005698</v>
+        <v>88.91591594482476</v>
       </c>
       <c r="G1957">
-        <v>32.04030141310673</v>
+        <v>32.04240681842172</v>
       </c>
       <c r="H1957">
         <v>18.860965237888</v>
@@ -77956,13 +77944,13 @@
         <v>3.179984016393442</v>
       </c>
       <c r="J1957">
-        <v>48.29921433803307</v>
+        <v>48.30223062740532</v>
       </c>
       <c r="K1957">
-        <v>62.75151239264812</v>
+        <v>62.75563314040304</v>
       </c>
       <c r="L1957">
-        <v>77.27735929591299</v>
+        <v>77.28192845919236</v>
       </c>
     </row>
     <row r="1958" spans="1:12">
@@ -77973,7 +77961,7 @@
         <v>1.950160448929444</v>
       </c>
       <c r="C1958">
-        <v>0.3699568101684226</v>
+        <v>0.3701166791593514</v>
       </c>
       <c r="D1958">
         <v>11.39848720882956</v>
@@ -77982,10 +77970,10 @@
         <v>14.52777677369059</v>
       </c>
       <c r="F1958">
-        <v>87.0828223039539</v>
+        <v>86.9937830269531</v>
       </c>
       <c r="G1958">
-        <v>31.7909464614444</v>
+        <v>31.79303548135672</v>
       </c>
       <c r="H1958">
         <v>18.99341285308064</v>
@@ -77994,13 +77982,13 @@
         <v>3.134061148409878</v>
       </c>
       <c r="J1958">
-        <v>48.02691132307814</v>
+        <v>48.02991060710772</v>
       </c>
       <c r="K1958">
-        <v>61.81004180239489</v>
+        <v>61.81410072593756</v>
       </c>
       <c r="L1958">
-        <v>76.36956206666223</v>
+        <v>76.37407755479272</v>
       </c>
     </row>
     <row r="1959" spans="1:12">
@@ -78011,7 +77999,7 @@
         <v>1.905634714840621</v>
       </c>
       <c r="C1959">
-        <v>0.3613363825574624</v>
+        <v>0.3614925264133871</v>
       </c>
       <c r="D1959">
         <v>11.13990231184788</v>
@@ -78020,10 +78008,10 @@
         <v>14.31569180414489</v>
       </c>
       <c r="F1959">
-        <v>87.44976297016117</v>
+        <v>87.36034850858599</v>
       </c>
       <c r="G1959">
-        <v>31.42421174895885</v>
+        <v>31.42627667030846</v>
       </c>
       <c r="H1959">
         <v>19.18430745979466</v>
@@ -78032,13 +78020,13 @@
         <v>3.145224800655289</v>
       </c>
       <c r="J1959">
-        <v>47.62125734606051</v>
+        <v>47.62423129697036</v>
       </c>
       <c r="K1959">
-        <v>61.20709706850414</v>
+        <v>61.21111639805037</v>
       </c>
       <c r="L1959">
-        <v>75.89097847798647</v>
+        <v>75.89546566899891</v>
       </c>
     </row>
     <row r="1960" spans="1:12">
@@ -78049,7 +78037,7 @@
         <v>1.893367226076143</v>
       </c>
       <c r="C1960">
-        <v>0.3670635838549859</v>
+        <v>0.3672222025995115</v>
       </c>
       <c r="D1960">
         <v>11.29756082565713</v>
@@ -78058,10 +78046,10 @@
         <v>14.40627572721958</v>
       </c>
       <c r="F1960">
-        <v>86.71241701990387</v>
+        <v>86.62375646993344</v>
       </c>
       <c r="G1960">
-        <v>31.5713813117112</v>
+        <v>31.57345590374323</v>
       </c>
       <c r="H1960">
         <v>19.67771717410764</v>
@@ -78070,13 +78058,13 @@
         <v>3.084420096971831</v>
       </c>
       <c r="J1960">
-        <v>48.13932960435405</v>
+        <v>48.1423359089133</v>
       </c>
       <c r="K1960">
-        <v>60.90210969109922</v>
+        <v>60.90610899282456</v>
       </c>
       <c r="L1960">
-        <v>76.03860710933704</v>
+        <v>76.04310302915863</v>
       </c>
     </row>
     <row r="1961" spans="1:12">
@@ -78087,7 +78075,7 @@
         <v>1.891973080846471</v>
       </c>
       <c r="C1961">
-        <v>0.3635800796396312</v>
+        <v>0.3637371930616745</v>
       </c>
       <c r="D1961">
         <v>11.19860660520305</v>
@@ -78096,10 +78084,10 @@
         <v>14.34363528898706</v>
       </c>
       <c r="F1961">
-        <v>86.90522121050388</v>
+        <v>86.81636352468875</v>
       </c>
       <c r="G1961">
-        <v>31.46417484223118</v>
+        <v>31.46624238960194</v>
       </c>
       <c r="H1961">
         <v>19.67907502054774</v>
@@ -78108,13 +78096,13 @@
         <v>3.162126565790791</v>
       </c>
       <c r="J1961">
-        <v>47.98486735454705</v>
+        <v>47.98786401292781</v>
       </c>
       <c r="K1961">
-        <v>61.46246537600352</v>
+        <v>61.46650147500024</v>
       </c>
       <c r="L1961">
-        <v>76.669581759454</v>
+        <v>76.67411498679002</v>
       </c>
     </row>
     <row r="1962" spans="1:12">
@@ -78125,7 +78113,7 @@
         <v>1.902030994277355</v>
       </c>
       <c r="C1962">
-        <v>0.3665523966970002</v>
+        <v>0.3667107945428347</v>
       </c>
       <c r="D1962">
         <v>11.24250584732752</v>
@@ -78134,10 +78122,10 @@
         <v>14.34921882445478</v>
       </c>
       <c r="F1962">
-        <v>86.58308114498722</v>
+        <v>86.49455283662873</v>
       </c>
       <c r="G1962">
-        <v>31.47925364890685</v>
+        <v>31.48132218712346</v>
       </c>
       <c r="H1962">
         <v>19.67008883639554</v>
@@ -78146,13 +78134,13 @@
         <v>3.163006877314285</v>
       </c>
       <c r="J1962">
-        <v>48.00123577599776</v>
+        <v>48.00423345658761</v>
       </c>
       <c r="K1962">
-        <v>61.50047581985008</v>
+        <v>61.50451441490538</v>
       </c>
       <c r="L1962">
-        <v>76.70350275669936</v>
+        <v>76.70803798967553</v>
       </c>
     </row>
     <row r="1963" spans="1:12">
@@ -78163,7 +78151,7 @@
         <v>1.919309067848522</v>
       </c>
       <c r="C1963">
-        <v>0.3678313664725042</v>
+        <v>0.3679903169980079</v>
       </c>
       <c r="D1963">
         <v>11.23896108691427</v>
@@ -78172,10 +78160,10 @@
         <v>14.36590809516078</v>
       </c>
       <c r="F1963">
-        <v>86.42816698129673</v>
+        <v>86.33979706749606</v>
       </c>
       <c r="G1963">
-        <v>31.4389287800743</v>
+        <v>31.44099466849708</v>
       </c>
       <c r="H1963">
         <v>19.65395993182764</v>
@@ -78184,13 +78172,13 @@
         <v>3.184324240348057</v>
       </c>
       <c r="J1963">
-        <v>47.93298084528696</v>
+        <v>47.93597426335153</v>
       </c>
       <c r="K1963">
-        <v>61.62893775081113</v>
+        <v>61.63298478166652</v>
       </c>
       <c r="L1963">
-        <v>76.83197524640079</v>
+        <v>76.83651807554467</v>
       </c>
     </row>
     <row r="1964" spans="1:12">
@@ -78201,7 +78189,7 @@
         <v>1.910243237490347</v>
       </c>
       <c r="C1964">
-        <v>0.3689210802176452</v>
+        <v>0.3690805016398375</v>
       </c>
       <c r="D1964">
         <v>11.30871597382701</v>
@@ -78210,10 +78198,10 @@
         <v>14.3700646984835</v>
       </c>
       <c r="F1964">
-        <v>87.21456308409763</v>
+        <v>87.12538910654965</v>
       </c>
       <c r="G1964">
-        <v>31.60469387915856</v>
+        <v>31.60677066019798</v>
       </c>
       <c r="H1964">
         <v>19.86416122170113</v>
@@ -78222,13 +78210,13 @@
         <v>3.163722174560724</v>
       </c>
       <c r="J1964">
-        <v>48.3012381444947</v>
+        <v>48.3042545602538</v>
       </c>
       <c r="K1964">
-        <v>61.75451822774463</v>
+        <v>61.75857350518163</v>
       </c>
       <c r="L1964">
-        <v>77.17831043502778</v>
+        <v>77.1828737418645</v>
       </c>
     </row>
     <row r="1965" spans="1:12">
@@ -78239,7 +78227,7 @@
         <v>1.936512947172796</v>
       </c>
       <c r="C1965">
-        <v>0.3756643244250567</v>
+        <v>0.3758266597972491</v>
       </c>
       <c r="D1965">
         <v>11.52266892807224</v>
@@ -78248,10 +78236,10 @@
         <v>14.54797524294503</v>
       </c>
       <c r="F1965">
-        <v>86.46049419507889</v>
+        <v>86.37209122778204</v>
       </c>
       <c r="G1965">
-        <v>31.74936281674893</v>
+        <v>31.75144910415181</v>
       </c>
       <c r="H1965">
         <v>19.76816195294703</v>
@@ -78260,13 +78248,13 @@
         <v>3.137032859070358</v>
       </c>
       <c r="J1965">
-        <v>48.45292246358458</v>
+        <v>48.4559483520402</v>
       </c>
       <c r="K1965">
-        <v>61.776714436083</v>
+        <v>61.78077117109405</v>
       </c>
       <c r="L1965">
-        <v>77.11002977753947</v>
+        <v>77.11458904715913</v>
       </c>
     </row>
     <row r="1966" spans="1:12">
@@ -78277,7 +78265,7 @@
         <v>1.89522349547216</v>
       </c>
       <c r="C1966">
-        <v>0.3693657419159614</v>
+        <v>0.3695253554892781</v>
       </c>
       <c r="D1966">
         <v>11.28524018289236</v>
@@ -78286,10 +78274,10 @@
         <v>14.32818179658527</v>
       </c>
       <c r="F1966">
-        <v>86.34017502622402</v>
+        <v>86.25189508125833</v>
       </c>
       <c r="G1966">
-        <v>31.43740806662014</v>
+        <v>31.43947385511507</v>
       </c>
       <c r="H1966">
         <v>20.31496453068164</v>
@@ -78298,13 +78286,13 @@
         <v>3.115408749356221</v>
       </c>
       <c r="J1966">
-        <v>48.33571125826541</v>
+        <v>48.33872982687291</v>
       </c>
       <c r="K1966">
-        <v>60.9568058468428</v>
+        <v>60.96080874033913</v>
       </c>
       <c r="L1966">
-        <v>76.72218756348801</v>
+        <v>76.72672390123708</v>
       </c>
     </row>
     <row r="1967" spans="1:12">
@@ -78315,7 +78303,7 @@
         <v>1.899391092311794</v>
       </c>
       <c r="C1967">
-        <v>0.370183460685107</v>
+        <v>0.3703434276182507</v>
       </c>
       <c r="D1967">
         <v>11.35338043956633</v>
@@ -78324,10 +78312,10 @@
         <v>14.41182516134657</v>
       </c>
       <c r="F1967">
-        <v>86.69676713900965</v>
+        <v>86.60812259051978</v>
       </c>
       <c r="G1967">
-        <v>31.60495249766111</v>
+        <v>31.60702929569466</v>
       </c>
       <c r="H1967">
         <v>20.28715139541067</v>
@@ -78336,13 +78324,13 @@
         <v>3.110099579411902</v>
       </c>
       <c r="J1967">
-        <v>48.56389031209802</v>
+        <v>48.56692313050368</v>
       </c>
       <c r="K1967">
-        <v>61.2297325268872</v>
+        <v>61.23375334285202</v>
       </c>
       <c r="L1967">
-        <v>77.00509038709353</v>
+        <v>77.00964345198241</v>
       </c>
     </row>
     <row r="1968" spans="1:12">
@@ -78353,7 +78341,7 @@
         <v>1.915089888342</v>
       </c>
       <c r="C1968">
-        <v>0.3708579861639075</v>
+        <v>0.3710182445789342</v>
       </c>
       <c r="D1968">
         <v>11.43852523797456</v>
@@ -78362,10 +78350,10 @@
         <v>14.5130720393173</v>
       </c>
       <c r="F1968">
-        <v>87.30547173437147</v>
+        <v>87.21620480576524</v>
       </c>
       <c r="G1968">
-        <v>31.83220904186402</v>
+        <v>31.83430077318829</v>
       </c>
       <c r="H1968">
         <v>20.24457693464679</v>
@@ -78374,13 +78362,13 @@
         <v>3.111324988131877</v>
       </c>
       <c r="J1968">
-        <v>48.87015173482546</v>
+        <v>48.87320367927875</v>
       </c>
       <c r="K1968">
-        <v>61.68206966171091</v>
+        <v>61.68612018161691</v>
       </c>
       <c r="L1968">
-        <v>77.47668022196632</v>
+        <v>77.48126117045494</v>
       </c>
     </row>
     <row r="1969" spans="1:12">
@@ -78391,7 +78379,7 @@
         <v>1.890029898189808</v>
       </c>
       <c r="C1969">
-        <v>0.3652209423587652</v>
+        <v>0.3653787648448397</v>
       </c>
       <c r="D1969">
         <v>11.4239173896577</v>
@@ -78400,10 +78388,10 @@
         <v>14.57662176529503</v>
       </c>
       <c r="F1969">
-        <v>89.14336249044808</v>
+        <v>89.05221637993436</v>
       </c>
       <c r="G1969">
-        <v>32.03313169449574</v>
+        <v>32.03523662868023</v>
       </c>
       <c r="H1969">
         <v>20.24487941605296</v>
@@ -78412,13 +78400,13 @@
         <v>3.104007715860152</v>
       </c>
       <c r="J1969">
-        <v>49.16337597645068</v>
+        <v>49.16644623277873</v>
       </c>
       <c r="K1969">
-        <v>61.99887000163286</v>
+        <v>62.00294132508987</v>
       </c>
       <c r="L1969">
-        <v>77.83509922088712</v>
+        <v>77.83970136154565</v>
       </c>
     </row>
     <row r="1970" spans="1:12">
@@ -78429,7 +78417,7 @@
         <v>1.897201302110704</v>
       </c>
       <c r="C1970">
-        <v>0.3685626633190812</v>
+        <v>0.3687219298590108</v>
       </c>
       <c r="D1970">
         <v>11.54372125835013</v>
@@ -78438,10 +78426,10 @@
         <v>14.70540766449057</v>
       </c>
       <c r="F1970">
-        <v>89.06680933376059</v>
+        <v>88.9757414962925</v>
       </c>
       <c r="G1970">
-        <v>32.21207916227732</v>
+        <v>32.21419585530718</v>
       </c>
       <c r="H1970">
         <v>20.24371974377022</v>
@@ -78450,13 +78438,13 @@
         <v>3.087068258501999</v>
       </c>
       <c r="J1970">
-        <v>49.42358237146588</v>
+        <v>49.42666887770181</v>
       </c>
       <c r="K1970">
-        <v>62.17604302919548</v>
+        <v>62.18012598719847</v>
       </c>
       <c r="L1970">
-        <v>78.03416971345509</v>
+        <v>78.03878362451562</v>
       </c>
     </row>
     <row r="1971" spans="1:12">
@@ -78467,7 +78455,7 @@
         <v>1.923369966295007</v>
       </c>
       <c r="C1971">
-        <v>0.3713847510716675</v>
+        <v>0.3715452371169796</v>
       </c>
       <c r="D1971">
         <v>11.64235314014846</v>
@@ -78476,10 +78464,10 @@
         <v>14.78255177721917</v>
       </c>
       <c r="F1971">
-        <v>88.95190949782361</v>
+        <v>88.86095914159979</v>
       </c>
       <c r="G1971">
-        <v>32.37448099837403</v>
+        <v>32.37660836301664</v>
       </c>
       <c r="H1971">
         <v>20.3655042415599</v>
@@ -78488,13 +78476,13 @@
         <v>3.105477475616139</v>
       </c>
       <c r="J1971">
-        <v>49.73463169224033</v>
+        <v>49.7377376235285</v>
       </c>
       <c r="K1971">
-        <v>62.67490073999605</v>
+        <v>62.67901645683958</v>
       </c>
       <c r="L1971">
-        <v>78.71501459634446</v>
+        <v>78.71966876358697</v>
       </c>
     </row>
     <row r="1972" spans="1:12">
@@ -78505,7 +78493,7 @@
         <v>1.860439112694154</v>
       </c>
       <c r="C1972">
-        <v>0.3608946604052405</v>
+        <v>0.3610506133803036</v>
       </c>
       <c r="D1972">
         <v>11.23921503811155</v>
@@ -78514,10 +78502,10 @@
         <v>14.31717269866237</v>
       </c>
       <c r="F1972">
-        <v>88.63444460902217</v>
+        <v>88.54381885004287</v>
       </c>
       <c r="G1972">
-        <v>31.66235628059186</v>
+        <v>31.66443685069448</v>
       </c>
       <c r="H1972">
         <v>20.52838471068509</v>
@@ -78526,13 +78514,13 @@
         <v>3.087253892876656</v>
       </c>
       <c r="J1972">
-        <v>48.79478673127111</v>
+        <v>48.79783396917458</v>
       </c>
       <c r="K1972">
-        <v>61.11237873117034</v>
+        <v>61.11639184078075</v>
       </c>
       <c r="L1972">
-        <v>77.10623222634057</v>
+        <v>77.11079127142314</v>
       </c>
     </row>
     <row r="1973" spans="1:12">
@@ -78543,7 +78531,7 @@
         <v>1.870669439422575</v>
       </c>
       <c r="C1973">
-        <v>0.3612233418952246</v>
+        <v>0.3613794369030243</v>
       </c>
       <c r="D1973">
         <v>11.27595556046125</v>
@@ -78552,10 +78540,10 @@
         <v>14.33378679605467</v>
       </c>
       <c r="F1973">
-        <v>88.76091320273012</v>
+        <v>88.67015813383816</v>
       </c>
       <c r="G1973">
-        <v>31.63820918512736</v>
+        <v>31.64028816849637</v>
       </c>
       <c r="H1973">
         <v>20.62924390441479</v>
@@ -78564,13 +78552,13 @@
         <v>3.108047953757737</v>
       </c>
       <c r="J1973">
-        <v>48.81936846990927</v>
+        <v>48.82241724294406</v>
       </c>
       <c r="K1973">
-        <v>61.27158161306318</v>
+        <v>61.27560517716135</v>
       </c>
       <c r="L1973">
-        <v>77.38172239096015</v>
+        <v>77.3862977248957</v>
       </c>
     </row>
     <row r="1974" spans="1:12">
@@ -78581,7 +78569,7 @@
         <v>1.887072020880431</v>
       </c>
       <c r="C1974">
-        <v>0.3643048869103353</v>
+        <v>0.364462313542472</v>
       </c>
       <c r="D1974">
         <v>11.37061587802937</v>
@@ -78590,10 +78578,10 @@
         <v>14.33237140678164</v>
       </c>
       <c r="F1974">
-        <v>88.67815097758323</v>
+        <v>88.587480530302</v>
       </c>
       <c r="G1974">
-        <v>31.72230212903674</v>
+        <v>31.72438663825049</v>
       </c>
       <c r="H1974">
         <v>20.57232730974048</v>
@@ -78602,13 +78590,13 @@
         <v>3.105281088102223</v>
       </c>
       <c r="J1974">
-        <v>48.90896671979554</v>
+        <v>48.91202108824741</v>
       </c>
       <c r="K1974">
-        <v>61.40716595151139</v>
+        <v>61.4111984191218</v>
       </c>
       <c r="L1974">
-        <v>77.48245805230104</v>
+        <v>77.48703934241429</v>
       </c>
     </row>
     <row r="1975" spans="1:12">
@@ -78619,7 +78607,7 @@
         <v>1.897554608048281</v>
       </c>
       <c r="C1975">
-        <v>0.3690263140729519</v>
+        <v>0.3691857809697235</v>
       </c>
       <c r="D1975">
         <v>11.51018970131265</v>
@@ -78628,10 +78616,10 @@
         <v>14.48258566327899</v>
       </c>
       <c r="F1975">
-        <v>87.7576670949186</v>
+        <v>87.66793781166072</v>
       </c>
       <c r="G1975">
-        <v>31.77933484694141</v>
+        <v>31.78142310384111</v>
       </c>
       <c r="H1975">
         <v>20.55551068312445</v>
@@ -78640,13 +78628,13 @@
         <v>3.090063291531363</v>
       </c>
       <c r="J1975">
-        <v>48.98250726786193</v>
+        <v>48.98556622892625</v>
       </c>
       <c r="K1975">
-        <v>61.36710179582501</v>
+        <v>61.3711316325143</v>
       </c>
       <c r="L1975">
-        <v>77.42112674456892</v>
+        <v>77.42570440835796</v>
       </c>
     </row>
     <row r="1976" spans="1:12">
@@ -78657,7 +78645,7 @@
         <v>1.98310622760831</v>
       </c>
       <c r="C1976">
-        <v>0.3782379074437444</v>
+        <v>0.3784013549352681</v>
       </c>
       <c r="D1976">
         <v>11.74615609411139</v>
@@ -78666,10 +78654,10 @@
         <v>14.66685390489605</v>
       </c>
       <c r="F1976">
-        <v>87.20810166503486</v>
+        <v>87.11893429407205</v>
       </c>
       <c r="G1976">
-        <v>32.23921086944511</v>
+        <v>32.24132934533088</v>
       </c>
       <c r="H1976">
         <v>21.17702517723456</v>
@@ -78678,13 +78666,13 @@
         <v>3.147673660572246</v>
       </c>
       <c r="J1976">
-        <v>50.02614546144516</v>
+        <v>50.02926959778894</v>
       </c>
       <c r="K1976">
-        <v>62.82719631762659</v>
+        <v>62.83132203537107</v>
       </c>
       <c r="L1976">
-        <v>79.66420932630172</v>
+        <v>79.668919616395</v>
       </c>
     </row>
     <row r="1977" spans="1:12">
@@ -78695,7 +78683,7 @@
         <v>1.959886961390883</v>
       </c>
       <c r="C1977">
-        <v>0.3745481601422411</v>
+        <v>0.374710013187706</v>
       </c>
       <c r="D1977">
         <v>11.65529355127468</v>
@@ -78704,10 +78692,10 @@
         <v>14.55111675564941</v>
       </c>
       <c r="F1977">
-        <v>87.37879438978389</v>
+        <v>87.28945249121162</v>
       </c>
       <c r="G1977">
-        <v>32.17891789686332</v>
+        <v>32.18103241082803</v>
       </c>
       <c r="H1977">
         <v>21.20199749912587</v>
@@ -78716,13 +78704,13 @@
         <v>3.135269404202839</v>
       </c>
       <c r="J1977">
-        <v>49.9520136161994</v>
+        <v>49.95513312300417</v>
       </c>
       <c r="K1977">
-        <v>62.58590470366475</v>
+        <v>62.59001457634288</v>
       </c>
       <c r="L1977">
-        <v>79.41233503213175</v>
+        <v>79.417030429703</v>
       </c>
     </row>
     <row r="1978" spans="1:12">
@@ -78733,7 +78721,7 @@
         <v>1.956919191515254</v>
       </c>
       <c r="C1978">
-        <v>0.3760314771120665</v>
+        <v>0.3761939711415075</v>
       </c>
       <c r="D1978">
         <v>11.85227332620764</v>
@@ -78742,10 +78730,10 @@
         <v>14.77722014790234</v>
       </c>
       <c r="F1978">
-        <v>88.82184197076914</v>
+        <v>88.73102460424707</v>
       </c>
       <c r="G1978">
-        <v>32.65385991891886</v>
+        <v>32.65600564187393</v>
       </c>
       <c r="H1978">
         <v>21.15819656928926</v>
@@ -78754,13 +78742,13 @@
         <v>3.124236986314085</v>
       </c>
       <c r="J1978">
-        <v>50.62661421447307</v>
+        <v>50.6297758501332</v>
       </c>
       <c r="K1978">
-        <v>63.3995221212239</v>
+        <v>63.40368542228995</v>
       </c>
       <c r="L1978">
-        <v>80.30044587505937</v>
+        <v>80.30519378378639</v>
       </c>
     </row>
     <row r="1979" spans="1:12">
@@ -78771,7 +78759,7 @@
         <v>1.922715643698621</v>
       </c>
       <c r="C1979">
-        <v>0.3694591923838239</v>
+        <v>0.3696188463397788</v>
       </c>
       <c r="D1979">
         <v>11.65017321583113</v>
@@ -78780,10 +78768,10 @@
         <v>14.54908819969317</v>
       </c>
       <c r="F1979">
-        <v>88.93728924484964</v>
+        <v>88.84635383734607</v>
       </c>
       <c r="G1979">
-        <v>32.41090773973738</v>
+        <v>32.41303749802336</v>
       </c>
       <c r="H1979">
         <v>21.27005867904345</v>
@@ -78792,13 +78780,13 @@
         <v>3.110122218653665</v>
       </c>
       <c r="J1979">
-        <v>50.33568927980582</v>
+        <v>50.33883274718308</v>
       </c>
       <c r="K1979">
-        <v>62.78460109819096</v>
+        <v>62.78872401880516</v>
       </c>
       <c r="L1979">
-        <v>79.70562083171794</v>
+        <v>79.71033357034119</v>
       </c>
     </row>
     <row r="1980" spans="1:12">
@@ -78809,7 +78797,7 @@
         <v>1.894986780493987</v>
       </c>
       <c r="C1980">
-        <v>0.366667739158013</v>
+        <v>0.3668261868466466</v>
       </c>
       <c r="D1980">
         <v>11.60500491674173</v>
@@ -78818,10 +78806,10 @@
         <v>14.50050571364386</v>
       </c>
       <c r="F1980">
-        <v>88.6353840348185</v>
+        <v>88.54475731530773</v>
       </c>
       <c r="G1980">
-        <v>32.30511992103592</v>
+        <v>32.30724272788181</v>
       </c>
       <c r="H1980">
         <v>21.21596855200841</v>
@@ -78830,13 +78818,13 @@
         <v>3.083023179044179</v>
       </c>
       <c r="J1980">
-        <v>50.1476092846037</v>
+        <v>50.15074100637187</v>
       </c>
       <c r="K1980">
-        <v>62.30614822867755</v>
+        <v>62.31023973039023</v>
       </c>
       <c r="L1980">
-        <v>79.10828740509307</v>
+        <v>79.11296482529987</v>
       </c>
     </row>
     <row r="1981" spans="1:12">
@@ -78847,7 +78835,7 @@
         <v>1.924993760384105</v>
       </c>
       <c r="C1981">
-        <v>0.3753450810284033</v>
+        <v>0.3755072784463312</v>
       </c>
       <c r="D1981">
         <v>12.04798289111295</v>
@@ -78856,10 +78844,10 @@
         <v>15.03859064810828</v>
       </c>
       <c r="F1981">
-        <v>89.85355235692411</v>
+        <v>89.76168010099416</v>
       </c>
       <c r="G1981">
-        <v>33.27875909937978</v>
+        <v>33.28094588518375</v>
       </c>
       <c r="H1981">
         <v>21.43541572345578</v>
@@ -78868,13 +78856,13 @@
         <v>3.067572524324741</v>
       </c>
       <c r="J1981">
-        <v>51.71310634823578</v>
+        <v>51.71633583540698</v>
       </c>
       <c r="K1981">
-        <v>64.02785943248371</v>
+        <v>64.03206399501846</v>
       </c>
       <c r="L1981">
-        <v>81.28025691911103</v>
+        <v>81.28506276093366</v>
       </c>
     </row>
     <row r="1982" spans="1:12">
@@ -78885,7 +78873,7 @@
         <v>1.912743230304631</v>
       </c>
       <c r="C1982">
-        <v>0.3748266070813784</v>
+        <v>0.3749885804517839</v>
       </c>
       <c r="D1982">
         <v>11.95837967223941</v>
@@ -78894,10 +78882,10 @@
         <v>14.92674569102539</v>
       </c>
       <c r="F1982">
-        <v>88.78014185740078</v>
+        <v>88.68936712785172</v>
       </c>
       <c r="G1982">
-        <v>33.13574233265584</v>
+        <v>33.13791972066243</v>
       </c>
       <c r="H1982">
         <v>21.38112396334213</v>
@@ -78906,13 +78894,13 @@
         <v>3.021714511915386</v>
       </c>
       <c r="J1982">
-        <v>51.46923438618823</v>
+        <v>51.47244864353804</v>
       </c>
       <c r="K1982">
-        <v>63.27411188374868</v>
+        <v>63.27826694941235</v>
       </c>
       <c r="L1982">
-        <v>80.3676288237087</v>
+        <v>80.37238070474878</v>
       </c>
     </row>
     <row r="1983" spans="1:12">
@@ -78923,7 +78911,7 @@
         <v>1.915992938318445</v>
       </c>
       <c r="C1983">
-        <v>0.3747548878832716</v>
+        <v>0.3749168302617463</v>
       </c>
       <c r="D1983">
         <v>11.9843924046299</v>
@@ -78932,10 +78920,10 @@
         <v>14.96296146173329</v>
       </c>
       <c r="F1983">
-        <v>88.90806406054092</v>
+        <v>88.81715853481211</v>
       </c>
       <c r="G1983">
-        <v>33.20248206312498</v>
+        <v>33.20466383667654</v>
       </c>
       <c r="H1983">
         <v>21.53222586510273</v>
@@ -78944,13 +78932,13 @@
         <v>3.012660669505731</v>
       </c>
       <c r="J1983">
-        <v>51.65865105630294</v>
+        <v>51.66187714273729</v>
       </c>
       <c r="K1983">
-        <v>63.3067613966916</v>
+        <v>63.31091860637382</v>
       </c>
       <c r="L1983">
-        <v>80.54694254850629</v>
+        <v>80.55170503179384</v>
       </c>
     </row>
     <row r="1984" spans="1:12">
@@ -78961,7 +78949,7 @@
         <v>1.817985164623273</v>
       </c>
       <c r="C1984">
-        <v>0.3513747104623197</v>
+        <v>0.3515265495928764</v>
       </c>
       <c r="D1984">
         <v>11.297669118338</v>
@@ -78970,10 +78958,10 @@
         <v>14.15663927513534</v>
       </c>
       <c r="F1984">
-        <v>88.84356545987764</v>
+        <v>88.75272588181357</v>
       </c>
       <c r="G1984">
-        <v>31.96534139585965</v>
+        <v>31.96744187546511</v>
       </c>
       <c r="H1984">
         <v>21.57588501197862</v>
@@ -78982,13 +78970,13 @@
         <v>3.052963812307657</v>
       </c>
       <c r="J1984">
-        <v>49.85625187492122</v>
+        <v>49.85936540139843</v>
       </c>
       <c r="K1984">
-        <v>61.37137709942662</v>
+        <v>61.37540721686527</v>
       </c>
       <c r="L1984">
-        <v>78.37157352503297</v>
+        <v>78.37620738570257</v>
       </c>
     </row>
     <row r="1985" spans="1:12">
@@ -78999,7 +78987,7 @@
         <v>1.924109788928293</v>
       </c>
       <c r="C1985">
-        <v>0.361617801927912</v>
+        <v>0.3617740673932505</v>
       </c>
       <c r="D1985">
         <v>11.54237616868518</v>
@@ -79008,10 +78996,10 @@
         <v>14.39476842552258</v>
       </c>
       <c r="F1985">
-        <v>88.21361389746183</v>
+        <v>88.12341842382823</v>
       </c>
       <c r="G1985">
-        <v>32.30052014079544</v>
+        <v>32.30264264538444</v>
       </c>
       <c r="H1985">
         <v>21.95443094458572</v>
@@ -79020,13 +79008,13 @@
         <v>3.145074914129441</v>
       </c>
       <c r="J1985">
-        <v>50.57157061059125</v>
+        <v>50.57472880877441</v>
       </c>
       <c r="K1985">
-        <v>62.94071771876046</v>
+        <v>62.94485089119471</v>
       </c>
       <c r="L1985">
-        <v>80.51897879510715</v>
+        <v>80.52373962498733</v>
       </c>
     </row>
     <row r="1986" spans="1:12">
@@ -79037,7 +79025,7 @@
         <v>1.861169042761186</v>
       </c>
       <c r="C1986">
-        <v>0.3453201535843581</v>
+        <v>0.3454693763665413</v>
       </c>
       <c r="D1986">
         <v>11.22492381400451</v>
@@ -79046,10 +79034,10 @@
         <v>13.99998573082802</v>
       </c>
       <c r="F1986">
-        <v>91.17873191783954</v>
+        <v>91.08550471007318</v>
       </c>
       <c r="G1986">
-        <v>32.28949344778168</v>
+        <v>32.2916152277939</v>
       </c>
       <c r="H1986">
         <v>21.76751845435463</v>
@@ -79058,13 +79046,13 @@
         <v>3.197591311190874</v>
       </c>
       <c r="J1986">
-        <v>50.44753253208028</v>
+        <v>50.45068298407661</v>
       </c>
       <c r="K1986">
-        <v>63.4447225439285</v>
+        <v>63.44888881320253</v>
       </c>
       <c r="L1986">
-        <v>80.92788929952644</v>
+        <v>80.93267430697789</v>
       </c>
     </row>
     <row r="1987" spans="1:12">
@@ -79075,7 +79063,7 @@
         <v>1.8724232500967</v>
       </c>
       <c r="C1987">
-        <v>0.3471273575615721</v>
+        <v>0.3472773612886341</v>
       </c>
       <c r="D1987">
         <v>11.28532508954864</v>
@@ -79084,10 +79072,10 @@
         <v>14.06548810314204</v>
       </c>
       <c r="F1987">
-        <v>90.73130368128504</v>
+        <v>90.63853395394523</v>
       </c>
       <c r="G1987">
-        <v>32.10558309759571</v>
+        <v>32.10769279264581</v>
       </c>
       <c r="H1987">
         <v>21.74465438468763</v>
@@ -79096,13 +79084,13 @@
         <v>3.187335234033466</v>
       </c>
       <c r="J1987">
-        <v>50.16131936961733</v>
+        <v>50.1644519475813</v>
       </c>
       <c r="K1987">
-        <v>62.98161472112277</v>
+        <v>62.98575057916928</v>
       </c>
       <c r="L1987">
-        <v>80.37498626987365</v>
+        <v>80.37973858593601</v>
       </c>
     </row>
     <row r="1988" spans="1:12">
@@ -79113,7 +79101,7 @@
         <v>1.870953497396388</v>
       </c>
       <c r="C1988">
-        <v>0.3416031893453118</v>
+        <v>0.3417508059202138</v>
       </c>
       <c r="D1988">
         <v>11.19794791768893</v>
@@ -79122,10 +79110,10 @@
         <v>13.9104890063537</v>
       </c>
       <c r="F1988">
-        <v>93.3402547530019</v>
+        <v>93.24481746033739</v>
       </c>
       <c r="G1988">
-        <v>32.1446817252237</v>
+        <v>32.14679398948991</v>
       </c>
       <c r="H1988">
         <v>21.82006259644319</v>
@@ -79134,13 +79122,13 @@
         <v>3.270248066572978</v>
       </c>
       <c r="J1988">
-        <v>50.26284073385063</v>
+        <v>50.26597965183102</v>
       </c>
       <c r="K1988">
-        <v>63.87749171250701</v>
+        <v>63.88168640073879</v>
       </c>
       <c r="L1988">
-        <v>81.47362816903063</v>
+        <v>81.47844544427727</v>
       </c>
     </row>
     <row r="1989" spans="1:12">
@@ -79151,7 +79139,7 @@
         <v>1.825970585424343</v>
       </c>
       <c r="C1989">
-        <v>0.3109159013199471</v>
+        <v>0.3110502570340241</v>
       </c>
       <c r="D1989">
         <v>10.44394170066912</v>
@@ -79160,10 +79148,10 @@
         <v>13.32590806838263</v>
       </c>
       <c r="F1989">
-        <v>96.91487132547329</v>
+        <v>96.81577910676542</v>
       </c>
       <c r="G1989">
-        <v>31.3851630019207</v>
+        <v>31.38722535733193</v>
       </c>
       <c r="H1989">
         <v>22.10454508460731</v>
@@ -79172,13 +79160,13 @@
         <v>3.456585706571588</v>
       </c>
       <c r="J1989">
-        <v>49.29843205581557</v>
+        <v>49.30151074640539</v>
       </c>
       <c r="K1989">
-        <v>64.18804507115871</v>
+        <v>64.1922601527166</v>
       </c>
       <c r="L1989">
-        <v>82.09567495494989</v>
+        <v>82.10052900983493</v>
       </c>
     </row>
     <row r="1990" spans="1:12">
@@ -79189,7 +79177,7 @@
         <v>1.831930149979357</v>
       </c>
       <c r="C1990">
-        <v>0.3124024403597288</v>
+        <v>0.312537438450131</v>
       </c>
       <c r="D1990">
         <v>10.55419391420462</v>
@@ -79198,10 +79186,10 @@
         <v>13.40153800353564</v>
       </c>
       <c r="F1990">
-        <v>97.19790692966576</v>
+        <v>97.09852531650677</v>
       </c>
       <c r="G1990">
-        <v>31.64935353431554</v>
+        <v>31.65143324999265</v>
       </c>
       <c r="H1990">
         <v>22.10536606638461</v>
@@ -79210,13 +79198,13 @@
         <v>3.463509101688168</v>
       </c>
       <c r="J1990">
-        <v>49.69311971472289</v>
+        <v>49.69622305358509</v>
       </c>
       <c r="K1990">
-        <v>64.79264302478745</v>
+        <v>64.79689780890493</v>
       </c>
       <c r="L1990">
-        <v>82.79238285944463</v>
+        <v>82.7972781084414</v>
       </c>
     </row>
     <row r="1991" spans="1:12">
@@ -79227,7 +79215,7 @@
         <v>1.830491488201552</v>
       </c>
       <c r="C1991">
-        <v>0.3140741016301762</v>
+        <v>0.3142098220935506</v>
       </c>
       <c r="D1991">
         <v>10.59597108405677</v>
@@ -79236,10 +79224,10 @@
         <v>13.44630625597392</v>
       </c>
       <c r="F1991">
-        <v>97.41183673600632</v>
+        <v>97.31223638676617</v>
       </c>
       <c r="G1991">
-        <v>31.58375397094172</v>
+        <v>31.58582937599554</v>
       </c>
       <c r="H1991">
         <v>22.27115273414681</v>
@@ -79248,13 +79236,13 @@
         <v>3.452179781005285</v>
       </c>
       <c r="J1991">
-        <v>49.68844339783043</v>
+        <v>49.69154644465631</v>
       </c>
       <c r="K1991">
-        <v>64.55237734555246</v>
+        <v>64.55661635197437</v>
       </c>
       <c r="L1991">
-        <v>82.6713037441628</v>
+        <v>82.67619183413845</v>
       </c>
     </row>
     <row r="1992" spans="1:12">
@@ -79265,7 +79253,7 @@
         <v>1.832544902310738</v>
       </c>
       <c r="C1992">
-        <v>0.3157362863104607</v>
+        <v>0.3158727250516996</v>
       </c>
       <c r="D1992">
         <v>10.5300382902287</v>
@@ -79274,10 +79262,10 @@
         <v>13.41895269384905</v>
       </c>
       <c r="F1992">
-        <v>95.34557530551291</v>
+        <v>95.24808763956665</v>
       </c>
       <c r="G1992">
-        <v>31.82030668752497</v>
+        <v>31.82239763673177</v>
       </c>
       <c r="H1992">
         <v>22.26463058613249</v>
@@ -79286,13 +79274,13 @@
         <v>3.431874844092579</v>
       </c>
       <c r="J1992">
-        <v>50.03834933000898</v>
+        <v>50.04147422848522</v>
       </c>
       <c r="K1992">
-        <v>64.84601382305765</v>
+        <v>64.8502721119129</v>
       </c>
       <c r="L1992">
-        <v>83.00370155575534</v>
+        <v>83.00860929935126</v>
       </c>
     </row>
     <row r="1993" spans="1:12">
@@ -79303,7 +79291,7 @@
         <v>1.775616716589282</v>
       </c>
       <c r="C1993">
-        <v>0.3062676264500658</v>
+        <v>0.3063999735107201</v>
       </c>
       <c r="D1993">
         <v>10.04997312097251</v>
@@ -79312,10 +79300,10 @@
         <v>13.1330198721882</v>
       </c>
       <c r="F1993">
-        <v>94.35522320882573</v>
+        <v>94.25874814481786</v>
       </c>
       <c r="G1993">
-        <v>31.12046036975402</v>
+        <v>31.12250533124871</v>
       </c>
       <c r="H1993">
         <v>21.59221903232394</v>
@@ -79324,13 +79312,13 @@
         <v>3.427183275080217</v>
       </c>
       <c r="J1993">
-        <v>48.61504663915491</v>
+        <v>48.61808265227684</v>
       </c>
       <c r="K1993">
-        <v>63.37548586709252</v>
+        <v>63.37964758975293</v>
       </c>
       <c r="L1993">
-        <v>80.68294062722916</v>
+        <v>80.68771115164846</v>
       </c>
     </row>
     <row r="1994" spans="1:12">
@@ -79341,7 +79329,7 @@
         <v>1.808819701990704</v>
       </c>
       <c r="C1994">
-        <v>0.3065514499391299</v>
+        <v>0.3066839196480867</v>
       </c>
       <c r="D1994">
         <v>10.08693436086268</v>
@@ -79350,10 +79338,10 @@
         <v>13.13269103287997</v>
       </c>
       <c r="F1994">
-        <v>95.18490239172259</v>
+        <v>95.08757900846376</v>
       </c>
       <c r="G1994">
-        <v>30.6548516601162</v>
+        <v>30.65686602592332</v>
       </c>
       <c r="H1994">
         <v>21.87526035100572</v>
@@ -79362,13 +79350,13 @@
         <v>3.495020862295596</v>
       </c>
       <c r="J1994">
-        <v>48.08337783080301</v>
+        <v>48.08638064117002</v>
       </c>
       <c r="K1994">
-        <v>63.05452011130548</v>
+        <v>63.05866075688157</v>
       </c>
       <c r="L1994">
-        <v>80.57959086953879</v>
+        <v>80.58435528321722</v>
       </c>
     </row>
     <row r="1995" spans="1:12">
@@ -79379,7 +79367,7 @@
         <v>1.861568985082521</v>
       </c>
       <c r="C1995">
-        <v>0.3106321996315048</v>
+        <v>0.3107664327499127</v>
       </c>
       <c r="D1995">
         <v>10.21304958992735</v>
@@ -79388,10 +79376,10 @@
         <v>13.10369852324724</v>
       </c>
       <c r="F1995">
-        <v>95.09335737885219</v>
+        <v>94.99612759731117</v>
       </c>
       <c r="G1995">
-        <v>30.66776647869573</v>
+        <v>30.66978169315053</v>
       </c>
       <c r="H1995">
         <v>21.81112743742978</v>
@@ -79400,13 +79388,13 @@
         <v>3.5613994886378</v>
       </c>
       <c r="J1995">
-        <v>48.06738020043357</v>
+        <v>48.07038201174743</v>
       </c>
       <c r="K1995">
-        <v>63.67986129441856</v>
+        <v>63.6840430047145</v>
       </c>
       <c r="L1995">
-        <v>81.23976191584353</v>
+        <v>81.24456536332603</v>
       </c>
     </row>
     <row r="1996" spans="1:12">
@@ -79417,7 +79405,7 @@
         <v>1.873722002723226</v>
       </c>
       <c r="C1996">
-        <v>0.3140413722692654</v>
+        <v>0.3141770785893405</v>
       </c>
       <c r="D1996">
         <v>10.23990185290774</v>
@@ -79426,10 +79414,10 @@
         <v>13.11733682060777</v>
       </c>
       <c r="F1996">
-        <v>93.51894611613855</v>
+        <v>93.423326117524</v>
       </c>
       <c r="G1996">
-        <v>30.61212735601599</v>
+        <v>30.6141389143596</v>
       </c>
       <c r="H1996">
         <v>21.87778744487961</v>
@@ -79438,13 +79426,13 @@
         <v>3.540972659297115</v>
       </c>
       <c r="J1996">
-        <v>48.02126042303141</v>
+        <v>48.02425935416189</v>
       </c>
       <c r="K1996">
-        <v>63.381708141483</v>
+        <v>63.38587027274587</v>
       </c>
       <c r="L1996">
-        <v>80.95950118780965</v>
+        <v>80.964288064371</v>
       </c>
     </row>
     <row r="1997" spans="1:12">
@@ -79455,7 +79443,7 @@
         <v>1.861213559309321</v>
       </c>
       <c r="C1997">
-        <v>0.3112311213914806</v>
+        <v>0.3113656133212275</v>
       </c>
       <c r="D1997">
         <v>10.1882988940172</v>
@@ -79464,10 +79452,10 @@
         <v>13.10113124508127</v>
       </c>
       <c r="F1997">
-        <v>94.67729710726866</v>
+        <v>94.58049273345777</v>
       </c>
       <c r="G1997">
-        <v>30.65461409620291</v>
+        <v>30.65662844639942</v>
       </c>
       <c r="H1997">
         <v>21.62824241917286</v>
@@ -79476,13 +79464,13 @@
         <v>3.547765419495585</v>
       </c>
       <c r="J1997">
-        <v>47.94764049081737</v>
+        <v>47.95063482437784</v>
       </c>
       <c r="K1997">
-        <v>63.53046953419094</v>
+        <v>63.53464143427296</v>
       </c>
       <c r="L1997">
-        <v>80.89965466558797</v>
+        <v>80.90443800361574</v>
       </c>
     </row>
     <row r="1998" spans="1:12">
@@ -79493,7 +79481,7 @@
         <v>1.896853649068134</v>
       </c>
       <c r="C1998">
-        <v>0.3138042501052155</v>
+        <v>0.3139398539579753</v>
       </c>
       <c r="D1998">
         <v>10.27379504724459</v>
@@ -79502,10 +79490,10 @@
         <v>13.11623396794742</v>
       </c>
       <c r="F1998">
-        <v>93.73162317656355</v>
+        <v>93.63578572275861</v>
       </c>
       <c r="G1998">
-        <v>30.69641323590579</v>
+        <v>30.69843033277219</v>
       </c>
       <c r="H1998">
         <v>21.54802560921435</v>
@@ -79514,13 +79502,13 @@
         <v>3.586788892337</v>
       </c>
       <c r="J1998">
-        <v>47.9652924540465</v>
+        <v>47.96828788997338</v>
       </c>
       <c r="K1998">
-        <v>63.96649674200564</v>
+        <v>63.97069727499336</v>
       </c>
       <c r="L1998">
-        <v>81.32435571241611</v>
+        <v>81.32916416165945</v>
       </c>
     </row>
     <row r="1999" spans="1:12">
@@ -79531,7 +79519,7 @@
         <v>2.00027618956258</v>
       </c>
       <c r="C1999">
-        <v>0.3222994529469768</v>
+        <v>0.322438727821512</v>
       </c>
       <c r="D1999">
         <v>10.52821637329838</v>
@@ -79540,10 +79528,10 @@
         <v>13.1726105177249</v>
       </c>
       <c r="F1999">
-        <v>93.12108695856716</v>
+        <v>93.02587375765162</v>
       </c>
       <c r="G1999">
-        <v>31.06012115016864</v>
+        <v>31.06216214670333</v>
       </c>
       <c r="H1999">
         <v>21.64822309403407</v>
@@ -79552,13 +79540,13 @@
         <v>3.713078206052222</v>
       </c>
       <c r="J1999">
-        <v>48.56095474183113</v>
+        <v>48.56398737691026</v>
       </c>
       <c r="K1999">
-        <v>65.85052341828342</v>
+        <v>65.85484767097766</v>
       </c>
       <c r="L1999">
-        <v>83.57464065368876</v>
+        <v>83.57958215508884</v>
       </c>
     </row>
     <row r="2000" spans="1:12">
@@ -79569,7 +79557,7 @@
         <v>2.119403885594109</v>
       </c>
       <c r="C2000">
-        <v>0.3393623246289584</v>
+        <v>0.3395089728616888</v>
       </c>
       <c r="D2000">
         <v>11.27848095588333</v>
@@ -79578,10 +79566,10 @@
         <v>13.60080791122023</v>
       </c>
       <c r="F2000">
-        <v>96.69182496421352</v>
+        <v>96.59296080295965</v>
       </c>
       <c r="G2000">
-        <v>32.37934697835514</v>
+        <v>32.38147466274693</v>
       </c>
       <c r="H2000">
         <v>21.6144164150482</v>
@@ -79590,13 +79578,13 @@
         <v>3.791321802243081</v>
       </c>
       <c r="J2000">
-        <v>50.50141286484342</v>
+        <v>50.50456668167043</v>
       </c>
       <c r="K2000">
-        <v>69.34122783281752</v>
+        <v>69.34578131205676</v>
       </c>
       <c r="L2000">
-        <v>87.52923849981751</v>
+        <v>87.53441382394948</v>
       </c>
     </row>
     <row r="2001" spans="1:12">
@@ -79607,7 +79595,7 @@
         <v>2.1117039359906</v>
       </c>
       <c r="C2001">
-        <v>0.3373001385172492</v>
+        <v>0.3374458956199782</v>
       </c>
       <c r="D2001">
         <v>11.18389581677465</v>
@@ -79616,10 +79604,10 @@
         <v>13.47748091206295</v>
       </c>
       <c r="F2001">
-        <v>96.74790743992583</v>
+        <v>96.64898593621385</v>
       </c>
       <c r="G2001">
-        <v>32.28236070626929</v>
+        <v>32.28448201758081</v>
       </c>
       <c r="H2001">
         <v>21.37606491822768</v>
@@ -79628,13 +79616,13 @@
         <v>3.799764854425847</v>
       </c>
       <c r="J2001">
-        <v>50.2184834954606</v>
+        <v>50.22161964332835</v>
       </c>
       <c r="K2001">
-        <v>69.21073859822413</v>
+        <v>69.21528350853491</v>
       </c>
       <c r="L2001">
-        <v>87.13968825176853</v>
+        <v>87.14484054303932</v>
       </c>
     </row>
     <row r="2002" spans="1:12">
@@ -79645,7 +79633,7 @@
         <v>2.168485853053899</v>
       </c>
       <c r="C2002">
-        <v>0.3565120960352237</v>
+        <v>0.3566661551780227</v>
       </c>
       <c r="D2002">
         <v>12.29815651463406</v>
@@ -79654,10 +79642,10 @@
         <v>14.78805818237426</v>
       </c>
       <c r="F2002">
-        <v>104.3666364429671</v>
+        <v>104.2599250433359</v>
       </c>
       <c r="G2002">
-        <v>35.00403148915067</v>
+        <v>35.00633164460158</v>
       </c>
       <c r="H2002">
         <v>20.99340398150138</v>
@@ -79666,13 +79654,13 @@
         <v>3.79091609667628</v>
       </c>
       <c r="J2002">
-        <v>54.01588150426511</v>
+        <v>54.01925479990873</v>
       </c>
       <c r="K2002">
-        <v>74.96519019267457</v>
+        <v>74.97011298461058</v>
       </c>
       <c r="L2002">
-        <v>93.27032936448997</v>
+        <v>93.27584414097643</v>
       </c>
     </row>
     <row r="2003" spans="1:12">
@@ -79683,7 +79671,7 @@
         <v>2.157104455580859</v>
       </c>
       <c r="C2003">
-        <v>0.355718327554867</v>
+        <v>0.3558720436874484</v>
       </c>
       <c r="D2003">
         <v>12.56437451457812</v>
@@ -79692,10 +79680,10 @@
         <v>15.10866797968917</v>
       </c>
       <c r="F2003">
-        <v>108.4826934249456</v>
+        <v>108.3717734945379</v>
       </c>
       <c r="G2003">
-        <v>36.37031280263978</v>
+        <v>36.37270273801823</v>
       </c>
       <c r="H2003">
         <v>20.88403853448928</v>
@@ -79704,13 +79692,13 @@
         <v>3.828983719288416</v>
       </c>
       <c r="J2003">
-        <v>55.94846866437314</v>
+        <v>55.95196265022243</v>
       </c>
       <c r="K2003">
-        <v>78.26763270618552</v>
+        <v>78.2727723619397</v>
       </c>
       <c r="L2003">
-        <v>96.84681122216529</v>
+        <v>96.85253746459368</v>
       </c>
     </row>
     <row r="2004" spans="1:12">
@@ -79721,7 +79709,7 @@
         <v>2.152527730465513</v>
       </c>
       <c r="C2004">
-        <v>0.3599431285384394</v>
+        <v>0.3600986703291829</v>
       </c>
       <c r="D2004">
         <v>12.35503422063418</v>
@@ -79730,10 +79718,10 @@
         <v>14.85103624558259</v>
       </c>
       <c r="F2004">
-        <v>105.4930660630879</v>
+        <v>105.385202926796</v>
       </c>
       <c r="G2004">
-        <v>35.64976250488229</v>
+        <v>35.65210509206614</v>
       </c>
       <c r="H2004">
         <v>21.09278390945823</v>
@@ -79742,13 +79730,13 @@
         <v>3.770575716599851</v>
       </c>
       <c r="J2004">
-        <v>55.03527449562908</v>
+        <v>55.03871145243755</v>
       </c>
       <c r="K2004">
-        <v>76.12007959695416</v>
+        <v>76.12507822782597</v>
       </c>
       <c r="L2004">
-        <v>94.69721256700977</v>
+        <v>94.70281171053973</v>
       </c>
     </row>
     <row r="2005" spans="1:12">
@@ -79759,7 +79747,7 @@
         <v>2.138772117091968</v>
       </c>
       <c r="C2005">
-        <v>0.356901563174242</v>
+        <v>0.3570557906170067</v>
       </c>
       <c r="D2005">
         <v>12.5082130245494</v>
@@ -79768,10 +79756,10 @@
         <v>15.03516070273712</v>
       </c>
       <c r="F2005">
-        <v>108.7379374071177</v>
+        <v>108.6267564982642</v>
       </c>
       <c r="G2005">
-        <v>36.62578514053116</v>
+        <v>36.62819186329283</v>
       </c>
       <c r="H2005">
         <v>21.25091506498745</v>
@@ -79780,13 +79768,13 @@
         <v>3.81005925204112</v>
       </c>
       <c r="J2005">
-        <v>56.56984641569812</v>
+        <v>56.5733792066322</v>
       </c>
       <c r="K2005">
-        <v>78.60264769706956</v>
+        <v>78.60780935248907</v>
       </c>
       <c r="L2005">
-        <v>97.65429296426797</v>
+        <v>97.66006695051109</v>
       </c>
     </row>
     <row r="2006" spans="1:12">
@@ -79797,7 +79785,7 @@
         <v>2.168764258132708</v>
       </c>
       <c r="C2006">
-        <v>0.3641815094242797</v>
+        <v>0.364338882741452</v>
       </c>
       <c r="D2006">
         <v>12.76042794881742</v>
@@ -79806,10 +79794,10 @@
         <v>15.33832886197425</v>
       </c>
       <c r="F2006">
-        <v>109.6017881150828</v>
+        <v>109.4897239477353</v>
       </c>
       <c r="G2006">
-        <v>37.27846475624504</v>
+        <v>37.28091436734019</v>
       </c>
       <c r="H2006">
         <v>21.24200045498155</v>
@@ -79818,13 +79806,13 @@
         <v>3.799088587922626</v>
       </c>
       <c r="J2006">
-        <v>57.52159660326364</v>
+        <v>57.52518883106465</v>
       </c>
       <c r="K2006">
-        <v>79.89020029453937</v>
+        <v>79.89544650058201</v>
       </c>
       <c r="L2006">
-        <v>99.0837173271334</v>
+        <v>99.08957583067071</v>
       </c>
     </row>
     <row r="2007" spans="1:12">
@@ -79835,7 +79823,7 @@
         <v>2.125305507975361</v>
       </c>
       <c r="C2007">
-        <v>0.3483367885605188</v>
+        <v>0.3484873149175423</v>
       </c>
       <c r="D2007">
         <v>12.44372370116853</v>
@@ -79844,10 +79832,10 @@
         <v>14.95815432546671</v>
       </c>
       <c r="F2007">
-        <v>110.854974456368</v>
+        <v>110.7416289478465</v>
       </c>
       <c r="G2007">
-        <v>36.62703582672466</v>
+        <v>36.62944263167036</v>
       </c>
       <c r="H2007">
         <v>20.53441669846221</v>
@@ -79856,13 +79844,13 @@
         <v>3.883146735704039</v>
       </c>
       <c r="J2007">
-        <v>56.08766443520098</v>
+        <v>56.09116711383606</v>
       </c>
       <c r="K2007">
-        <v>79.37796545255974</v>
+        <v>79.38317802131628</v>
       </c>
       <c r="L2007">
-        <v>97.68681409760366</v>
+        <v>97.69259000671747</v>
       </c>
     </row>
     <row r="2008" spans="1:12">
@@ -79873,7 +79861,7 @@
         <v>2.151443081237158</v>
       </c>
       <c r="C2008">
-        <v>0.3576619534489323</v>
+        <v>0.357816509478231</v>
       </c>
       <c r="D2008">
         <v>12.71754364104504</v>
@@ -79882,10 +79870,10 @@
         <v>15.28356814941348</v>
       </c>
       <c r="F2008">
-        <v>110.0174402742559</v>
+        <v>109.9049511164596</v>
       </c>
       <c r="G2008">
-        <v>37.19934888756173</v>
+        <v>37.20179329986151</v>
       </c>
       <c r="H2008">
         <v>20.46007607815845</v>
@@ -79894,13 +79882,13 @@
         <v>3.846478106380503</v>
       </c>
       <c r="J2008">
-        <v>56.86947498102904</v>
+        <v>56.87302648378834</v>
       </c>
       <c r="K2008">
-        <v>80.24349620009437</v>
+        <v>80.24876560626804</v>
       </c>
       <c r="L2008">
-        <v>98.55705237942401</v>
+        <v>98.56287974294618</v>
       </c>
     </row>
     <row r="2009" spans="1:12">
@@ -79911,7 +79899,7 @@
         <v>2.153187705956903</v>
       </c>
       <c r="C2009">
-        <v>0.3820513643429471</v>
+        <v>0.3822164597390091</v>
       </c>
       <c r="D2009">
         <v>13.53610502867477</v>
@@ -79920,10 +79908,10 @@
         <v>16.18844425897671</v>
       </c>
       <c r="F2009">
-        <v>114.207687621952</v>
+        <v>114.0909140762084</v>
       </c>
       <c r="G2009">
-        <v>39.66964220491082</v>
+        <v>39.67224894304558</v>
       </c>
       <c r="H2009">
         <v>20.5621734750344</v>
@@ -79932,13 +79920,13 @@
         <v>3.641037328086728</v>
       </c>
       <c r="J2009">
-        <v>60.52811985556275</v>
+        <v>60.53189984095481</v>
       </c>
       <c r="K2009">
-        <v>83.42931120261905</v>
+        <v>83.43478981394998</v>
       </c>
       <c r="L2009">
-        <v>102.2016115557313</v>
+        <v>102.2076544103897</v>
       </c>
     </row>
     <row r="2010" spans="1:12">
@@ -79949,7 +79937,7 @@
         <v>2.161236015214861</v>
       </c>
       <c r="C2010">
-        <v>0.3853192890833911</v>
+        <v>0.3854857966438365</v>
       </c>
       <c r="D2010">
         <v>13.38502002632434</v>
@@ -79958,10 +79946,10 @@
         <v>16.00775482625318</v>
       </c>
       <c r="F2010">
-        <v>111.8839289885675</v>
+        <v>111.7695314084067</v>
       </c>
       <c r="G2010">
-        <v>39.08359167739711</v>
+        <v>39.08615990547295</v>
       </c>
       <c r="H2010">
         <v>20.5770479512151</v>
@@ -79970,13 +79958,13 @@
         <v>3.626337595294043</v>
       </c>
       <c r="J2010">
-        <v>59.68957759550455</v>
+        <v>59.69330521387281</v>
       </c>
       <c r="K2010">
-        <v>82.02837508170026</v>
+        <v>82.03376169677237</v>
       </c>
       <c r="L2010">
-        <v>100.6755517357297</v>
+        <v>100.6815043593482</v>
       </c>
     </row>
     <row r="2011" spans="1:12">
@@ -79987,7 +79975,7 @@
         <v>2.163435697982202</v>
       </c>
       <c r="C2011">
-        <v>0.3886457797030464</v>
+        <v>0.3888137247358779</v>
       </c>
       <c r="D2011">
         <v>13.47735484460917</v>
@@ -79996,10 +79984,10 @@
         <v>16.11818223914635</v>
       </c>
       <c r="F2011">
-        <v>112.0177276844963</v>
+        <v>111.9031932996381</v>
       </c>
       <c r="G2011">
-        <v>39.19215966398286</v>
+        <v>39.19473502618684</v>
       </c>
       <c r="H2011">
         <v>20.84203827800707</v>
@@ -80008,13 +79996,13 @@
         <v>3.600807452325979</v>
       </c>
       <c r="J2011">
-        <v>60.03926526401544</v>
+        <v>60.04301472040348</v>
       </c>
       <c r="K2011">
-        <v>81.96748873512878</v>
+        <v>81.97287135193429</v>
       </c>
       <c r="L2011">
-        <v>100.9324209249736</v>
+        <v>100.9383887364462</v>
       </c>
     </row>
     <row r="2012" spans="1:12">
@@ -80025,7 +80013,7 @@
         <v>2.201534090454663</v>
       </c>
       <c r="C2012">
-        <v>0.3896925519550624</v>
+        <v>0.389860949328327</v>
       </c>
       <c r="D2012">
         <v>13.26960395972766</v>
@@ -80034,10 +80022,10 @@
         <v>15.86972349768913</v>
       </c>
       <c r="F2012">
-        <v>109.3990004597095</v>
+        <v>109.287143635966</v>
       </c>
       <c r="G2012">
-        <v>38.52160025713074</v>
+        <v>38.52413155609945</v>
       </c>
       <c r="H2012">
         <v>20.87570875246866</v>
@@ -80046,13 +80034,13 @@
         <v>3.637577595850289</v>
       </c>
       <c r="J2012">
-        <v>59.08763234489097</v>
+        <v>59.09132237173549</v>
       </c>
       <c r="K2012">
-        <v>80.98357475552994</v>
+        <v>80.98889276096327</v>
       </c>
       <c r="L2012">
-        <v>99.88277802574601</v>
+        <v>99.88868377518865</v>
       </c>
     </row>
     <row r="2013" spans="1:12">
@@ -80063,7 +80051,7 @@
         <v>2.173998132291945</v>
       </c>
       <c r="C2013">
-        <v>0.3829277954903225</v>
+        <v>0.383093269617521</v>
       </c>
       <c r="D2013">
         <v>12.99904265758897</v>
@@ -80072,10 +80060,10 @@
         <v>15.54614691867842</v>
       </c>
       <c r="F2013">
-        <v>107.8878805365694</v>
+        <v>107.7775687824718</v>
       </c>
       <c r="G2013">
-        <v>37.78573919817293</v>
+        <v>37.78822214285918</v>
       </c>
       <c r="H2013">
         <v>20.77745784509571</v>
@@ -80084,13 +80072,13 @@
         <v>3.620526973945642</v>
       </c>
       <c r="J2013">
-        <v>57.94582018194503</v>
+        <v>57.94943890253873</v>
       </c>
       <c r="K2013">
-        <v>79.24678198395007</v>
+        <v>79.25198593818939</v>
       </c>
       <c r="L2013">
-        <v>97.83735561591953</v>
+        <v>97.8431404260722</v>
       </c>
     </row>
     <row r="2014" spans="1:12">
@@ -80101,7 +80089,7 @@
         <v>2.155506099519271</v>
       </c>
       <c r="C2014">
-        <v>0.3761486830341942</v>
+        <v>0.3763112277116896</v>
       </c>
       <c r="D2014">
         <v>12.85780373885943</v>
@@ -80110,10 +80098,10 @@
         <v>15.37723286561753</v>
       </c>
       <c r="F2014">
-        <v>107.430318203646</v>
+        <v>107.3204742917498</v>
       </c>
       <c r="G2014">
-        <v>37.55804866192969</v>
+        <v>37.56051664480709</v>
       </c>
       <c r="H2014">
         <v>20.79937101324334</v>
@@ -80122,13 +80110,13 @@
         <v>3.660243037053594</v>
       </c>
       <c r="J2014">
-        <v>57.62938525915717</v>
+        <v>57.63298421836743</v>
       </c>
       <c r="K2014">
-        <v>79.20391051347985</v>
+        <v>79.20911165244814</v>
       </c>
       <c r="L2014">
-        <v>97.81551606485984</v>
+        <v>97.82129958370965</v>
       </c>
     </row>
     <row r="2015" spans="1:12">
@@ -80139,7 +80127,7 @@
         <v>2.112446585071384</v>
       </c>
       <c r="C2015">
-        <v>0.3674104982808318</v>
+        <v>0.3675692669370711</v>
       </c>
       <c r="D2015">
         <v>12.62682184833099</v>
@@ -80148,10 +80136,10 @@
         <v>15.1009911068744</v>
       </c>
       <c r="F2015">
-        <v>107.29440964221</v>
+        <v>107.1847046922782</v>
       </c>
       <c r="G2015">
-        <v>36.98638871344031</v>
+        <v>36.9888191318804</v>
       </c>
       <c r="H2015">
         <v>20.78250065956013</v>
@@ -80160,13 +80148,13 @@
         <v>3.649479281868668</v>
       </c>
       <c r="J2015">
-        <v>56.78439763756292</v>
+        <v>56.78794382723608</v>
       </c>
       <c r="K2015">
-        <v>77.88191290217361</v>
+        <v>77.88702722859379</v>
       </c>
       <c r="L2015">
-        <v>96.32630092773533</v>
+        <v>96.33199639405356</v>
       </c>
     </row>
     <row r="2016" spans="1:12">
@@ -80177,7 +80165,7 @@
         <v>2.144192536786246</v>
       </c>
       <c r="C2016">
-        <v>0.375476646560818</v>
+        <v>0.3756389008320014</v>
       </c>
       <c r="D2016">
         <v>12.94779403240388</v>
@@ -80186,10 +80174,10 @@
         <v>15.48485635463502</v>
       </c>
       <c r="F2016">
-        <v>108.4249441872965</v>
+        <v>108.3140833035552</v>
       </c>
       <c r="G2016">
-        <v>37.59032630902915</v>
+        <v>37.59279641290812</v>
       </c>
       <c r="H2016">
         <v>20.8278789734987</v>
@@ -80198,13 +80186,13 @@
         <v>3.630719128648556</v>
       </c>
       <c r="J2016">
-        <v>57.69624626628351</v>
+        <v>57.69984940096842</v>
       </c>
       <c r="K2016">
-        <v>78.95344293745542</v>
+        <v>78.95862762879301</v>
       </c>
       <c r="L2016">
-        <v>97.57164839900959</v>
+        <v>97.5774174987437</v>
       </c>
     </row>
     <row r="2017" spans="1:12">
@@ -80215,7 +80203,7 @@
         <v>2.139947919252219</v>
       </c>
       <c r="C2017">
-        <v>0.3774931381904941</v>
+        <v>0.3776562638457775</v>
       </c>
       <c r="D2017">
         <v>12.89006385448573</v>
@@ -80224,10 +80212,10 @@
         <v>15.41581420659399</v>
       </c>
       <c r="F2017">
-        <v>106.2775797283882</v>
+        <v>106.1689144530783</v>
       </c>
       <c r="G2017">
-        <v>37.37837134072042</v>
+        <v>37.38082751679293</v>
       </c>
       <c r="H2017">
         <v>20.75618973919575</v>
@@ -80236,13 +80224,13 @@
         <v>3.598386710121428</v>
       </c>
       <c r="J2017">
-        <v>57.33754181118695</v>
+        <v>57.34112254475311</v>
       </c>
       <c r="K2017">
-        <v>78.15671032418564</v>
+        <v>78.16184269592164</v>
       </c>
       <c r="L2017">
-        <v>96.60153749594461</v>
+        <v>96.60724923612146</v>
       </c>
     </row>
     <row r="2018" spans="1:12">
@@ -80253,7 +80241,7 @@
         <v>2.131191584895362</v>
       </c>
       <c r="C2018">
-        <v>0.3739775628384053</v>
+        <v>0.3741391693123447</v>
       </c>
       <c r="D2018">
         <v>12.72686220480829</v>
@@ -80262,10 +80250,10 @@
         <v>15.22063392370024</v>
       </c>
       <c r="F2018">
-        <v>105.1906911742901</v>
+        <v>105.0831372062217</v>
       </c>
       <c r="G2018">
-        <v>36.92881687927409</v>
+        <v>36.93124351460227</v>
       </c>
       <c r="H2018">
         <v>20.71270503774224</v>
@@ -80274,13 +80262,13 @@
         <v>3.604143142571687</v>
       </c>
       <c r="J2018">
-        <v>56.65238527546314</v>
+        <v>56.65592322095489</v>
       </c>
       <c r="K2018">
-        <v>77.27922421204032</v>
+        <v>77.28429896127786</v>
       </c>
       <c r="L2018">
-        <v>95.57482790744612</v>
+        <v>95.58047894156634</v>
       </c>
     </row>
     <row r="2019" spans="1:12">
@@ -80291,7 +80279,7 @@
         <v>2.148917650395374</v>
       </c>
       <c r="C2019">
-        <v>0.378176813843023</v>
+        <v>0.378340234934243</v>
       </c>
       <c r="D2019">
         <v>12.83855636328074</v>
@@ -80300,10 +80288,10 @@
         <v>15.35421405289205</v>
       </c>
       <c r="F2019">
-        <v>104.274572835074</v>
+        <v>104.1679555674065</v>
       </c>
       <c r="G2019">
-        <v>37.10799757152148</v>
+        <v>37.11043598102047</v>
       </c>
       <c r="H2019">
         <v>20.75382190561238</v>
@@ -80312,13 +80300,13 @@
         <v>3.609775769722759</v>
       </c>
       <c r="J2019">
-        <v>56.94163701618252</v>
+        <v>56.94519302546606</v>
       </c>
       <c r="K2019">
-        <v>77.71457410582373</v>
+        <v>77.71967744348932</v>
       </c>
       <c r="L2019">
-        <v>96.10683519623059</v>
+        <v>96.11251768624153</v>
       </c>
     </row>
     <row r="2020" spans="1:12">
@@ -80329,7 +80317,7 @@
         <v>2.163793950202906</v>
       </c>
       <c r="C2020">
-        <v>0.3796828720378739</v>
+        <v>0.3798469439402083</v>
       </c>
       <c r="D2020">
         <v>12.95657459878426</v>
@@ -80338,10 +80326,10 @@
         <v>15.49535743372016</v>
       </c>
       <c r="F2020">
-        <v>105.3166175126966</v>
+        <v>105.2089347891535</v>
       </c>
       <c r="G2020">
-        <v>37.37412051903772</v>
+        <v>37.37657641578382</v>
       </c>
       <c r="H2020">
         <v>20.84226723451947</v>
@@ -80350,13 +80338,13 @@
         <v>3.608535262818882</v>
       </c>
       <c r="J2020">
-        <v>57.39024660589858</v>
+        <v>57.39383063088292</v>
       </c>
       <c r="K2020">
-        <v>78.25855695034517</v>
+        <v>78.26369601011528</v>
       </c>
       <c r="L2020">
-        <v>96.81468011349554</v>
+        <v>96.8204044561142</v>
       </c>
     </row>
     <row r="2021" spans="1:12">
@@ -80367,7 +80355,7 @@
         <v>2.146686876705526</v>
       </c>
       <c r="C2021">
-        <v>0.3769831590688418</v>
+        <v>0.3771460643474615</v>
       </c>
       <c r="D2021">
         <v>12.879330053881</v>
@@ -80376,10 +80364,10 @@
         <v>15.40297716577547</v>
       </c>
       <c r="F2021">
-        <v>105.2030756896721</v>
+        <v>105.0955090588504</v>
       </c>
       <c r="G2021">
-        <v>37.27505422184085</v>
+        <v>37.27750360882582</v>
       </c>
       <c r="H2021">
         <v>20.71139847435781</v>
@@ -80388,13 +80376,13 @@
         <v>3.631007285185982</v>
       </c>
       <c r="J2021">
-        <v>57.15564191608333</v>
+        <v>57.15921128998809</v>
       </c>
       <c r="K2021">
-        <v>78.29479584356181</v>
+        <v>78.29993728305686</v>
       </c>
       <c r="L2021">
-        <v>96.70305352483578</v>
+        <v>96.70877126733102</v>
       </c>
     </row>
     <row r="2022" spans="1:12">
@@ -80405,7 +80393,7 @@
         <v>2.222593244169758</v>
       </c>
       <c r="C2022">
-        <v>0.4335320606323436</v>
+        <v>0.4337194023197079</v>
       </c>
       <c r="D2022">
         <v>14.03938311328127</v>
@@ -80414,10 +80402,10 @@
         <v>16.72979853572996</v>
       </c>
       <c r="F2022">
-        <v>94.66862148169956</v>
+        <v>94.57182597842586</v>
       </c>
       <c r="G2022">
-        <v>38.65415000883183</v>
+        <v>38.65669001779824</v>
       </c>
       <c r="H2022">
         <v>20.35204816775349</v>
@@ -80426,13 +80414,13 @@
         <v>3.37394411857212</v>
       </c>
       <c r="J2022">
-        <v>58.91662661813031</v>
+        <v>58.92030596565503</v>
       </c>
       <c r="K2022">
-        <v>78.42002790444498</v>
+        <v>78.42517756764197</v>
       </c>
       <c r="L2022">
-        <v>96.42280358910861</v>
+        <v>96.42850476132081</v>
       </c>
     </row>
     <row r="2023" spans="1:12">
@@ -80443,7 +80431,7 @@
         <v>2.141882622566381</v>
       </c>
       <c r="C2023">
-        <v>0.417464966945758</v>
+        <v>0.4176453655792731</v>
       </c>
       <c r="D2023">
         <v>13.74157273515965</v>
@@ -80452,10 +80440,10 @@
         <v>16.37491772739081</v>
       </c>
       <c r="F2023">
-        <v>93.26482311369824</v>
+        <v>93.1694629473651</v>
       </c>
       <c r="G2023">
-        <v>38.61582620129793</v>
+        <v>38.61836369196256</v>
       </c>
       <c r="H2023">
         <v>20.58918110062248</v>
@@ -80464,13 +80452,13 @@
         <v>3.325368510257059</v>
       </c>
       <c r="J2023">
-        <v>59.03275167927309</v>
+        <v>59.03643827881615</v>
       </c>
       <c r="K2023">
-        <v>77.77776062739906</v>
+        <v>77.78286811437847</v>
       </c>
       <c r="L2023">
-        <v>95.99293189270112</v>
+        <v>95.99860764797376</v>
       </c>
     </row>
     <row r="2024" spans="1:12">
@@ -80481,7 +80469,7 @@
         <v>2.140293452459169</v>
       </c>
       <c r="C2024">
-        <v>0.4175892053838337</v>
+        <v>0.4177696577043556</v>
       </c>
       <c r="D2024">
         <v>13.72444661758293</v>
@@ -80490,10 +80478,10 @@
         <v>16.35450967281705</v>
       </c>
       <c r="F2024">
-        <v>92.86031978384527</v>
+        <v>92.76537320865548</v>
       </c>
       <c r="G2024">
-        <v>38.52245465556587</v>
+        <v>38.52498601067809</v>
       </c>
       <c r="H2024">
         <v>20.63927661327943</v>
@@ -80502,13 +80490,13 @@
         <v>3.292489405220062</v>
       </c>
       <c r="J2024">
-        <v>58.93305788570994</v>
+        <v>58.9367382593685</v>
       </c>
       <c r="K2024">
-        <v>77.20518883156852</v>
+        <v>77.2102587190726</v>
       </c>
       <c r="L2024">
-        <v>95.41532318563628</v>
+        <v>95.42096478875209</v>
       </c>
     </row>
     <row r="2025" spans="1:12">
@@ -80519,7 +80507,7 @@
         <v>2.136228314341431</v>
       </c>
       <c r="C2025">
-        <v>0.4110236088329823</v>
+        <v>0.411201223970172</v>
       </c>
       <c r="D2025">
         <v>13.716447949687</v>
@@ -80528,10 +80516,10 @@
         <v>16.34497819259649</v>
       </c>
       <c r="F2025">
-        <v>92.96530499851868</v>
+        <v>92.87025107945368</v>
       </c>
       <c r="G2025">
-        <v>38.4852398050088</v>
+        <v>38.48776871469008</v>
       </c>
       <c r="H2025">
         <v>20.46278084863733</v>
@@ -80540,13 +80528,13 @@
         <v>3.326715217818747</v>
       </c>
       <c r="J2025">
-        <v>58.75298108956314</v>
+        <v>58.75665021741297</v>
       </c>
       <c r="K2025">
-        <v>77.53188277702803</v>
+        <v>77.53697411777348</v>
       </c>
       <c r="L2025">
-        <v>95.57471347428202</v>
+        <v>95.5803645016362</v>
       </c>
     </row>
     <row r="2026" spans="1:12">
@@ -80557,7 +80545,7 @@
         <v>2.129586869326896</v>
       </c>
       <c r="C2026">
-        <v>0.4127322826976044</v>
+        <v>0.4129106362019739</v>
       </c>
       <c r="D2026">
         <v>13.60476136946233</v>
@@ -80566,10 +80554,10 @@
         <v>16.21188872768006</v>
       </c>
       <c r="F2026">
-        <v>92.21717692675539</v>
+        <v>92.12288794365425</v>
       </c>
       <c r="G2026">
-        <v>38.20190031635914</v>
+        <v>38.20441060747446</v>
       </c>
       <c r="H2026">
         <v>20.6926050485999</v>
@@ -80578,13 +80566,13 @@
         <v>3.34424217948811</v>
       </c>
       <c r="J2026">
-        <v>58.5070209374299</v>
+        <v>58.51067470505072</v>
       </c>
       <c r="K2026">
-        <v>77.1653108432366</v>
+        <v>77.17037811204473</v>
       </c>
       <c r="L2026">
-        <v>95.43638036577526</v>
+        <v>95.44202321393485</v>
       </c>
     </row>
     <row r="2027" spans="1:12">
@@ -80595,7 +80583,7 @@
         <v>2.10988158396459</v>
       </c>
       <c r="C2027">
-        <v>0.4079858108708317</v>
+        <v>0.4081621132880455</v>
       </c>
       <c r="D2027">
         <v>13.45093491402231</v>
@@ -80604,10 +80592,10 @@
         <v>16.02858397787645</v>
       </c>
       <c r="F2027">
-        <v>91.49069273802242</v>
+        <v>91.39714656073761</v>
       </c>
       <c r="G2027">
-        <v>37.85448248184286</v>
+        <v>37.8569699437299</v>
       </c>
       <c r="H2027">
         <v>20.6279725488665</v>
@@ -80616,13 +80604,13 @@
         <v>3.348344517529978</v>
       </c>
       <c r="J2027">
-        <v>57.95586097367329</v>
+        <v>57.95948032131515</v>
       </c>
       <c r="K2027">
-        <v>76.51087864355935</v>
+        <v>76.51590293730736</v>
       </c>
       <c r="L2027">
-        <v>94.63340868794393</v>
+        <v>94.63900405895446</v>
       </c>
     </row>
     <row r="2028" spans="1:12">
@@ -80633,7 +80621,7 @@
         <v>2.11342029623534</v>
       </c>
       <c r="C2028">
-        <v>0.4153162655098669</v>
+        <v>0.4154957356276176</v>
       </c>
       <c r="D2028">
         <v>13.79759160639627</v>
@@ -80642,10 +80630,10 @@
         <v>16.44167168818992</v>
       </c>
       <c r="F2028">
-        <v>93.75752541693281</v>
+        <v>93.66166147895224</v>
       </c>
       <c r="G2028">
-        <v>38.84579586125753</v>
+        <v>38.84834846349487</v>
       </c>
       <c r="H2028">
         <v>20.40158078075271</v>
@@ -80654,13 +80642,13 @@
         <v>3.295807664154301</v>
       </c>
       <c r="J2028">
-        <v>59.23867661511969</v>
+        <v>59.24237607468964</v>
       </c>
       <c r="K2028">
-        <v>77.91426248382059</v>
+        <v>77.91937893456353</v>
       </c>
       <c r="L2028">
-        <v>95.93597163658464</v>
+        <v>95.94164402397938</v>
       </c>
     </row>
     <row r="2029" spans="1:12">
@@ -80671,7 +80659,7 @@
         <v>2.105703387946828</v>
       </c>
       <c r="C2029">
-        <v>0.4223233849700614</v>
+        <v>0.4225058830659075</v>
       </c>
       <c r="D2029">
         <v>13.90978499801382</v>
@@ -80680,10 +80668,10 @@
         <v>16.57536508651497</v>
       </c>
       <c r="F2029">
-        <v>94.33136515630592</v>
+        <v>94.23491448635966</v>
       </c>
       <c r="G2029">
-        <v>39.22467325930511</v>
+        <v>39.2272507580151</v>
       </c>
       <c r="H2029">
         <v>20.57152416940109</v>
@@ -80692,13 +80680,13 @@
         <v>3.26819416423937</v>
       </c>
       <c r="J2029">
-        <v>59.91092773059291</v>
+        <v>59.91466917229286</v>
       </c>
       <c r="K2029">
-        <v>78.3477917648535</v>
+        <v>78.35293668446901</v>
       </c>
       <c r="L2029">
-        <v>96.61618105148703</v>
+        <v>96.62189365749055</v>
       </c>
     </row>
     <row r="2030" spans="1:12">
@@ -80709,7 +80697,7 @@
         <v>2.112891043940854</v>
       </c>
       <c r="C2030">
-        <v>0.4227301652736168</v>
+        <v>0.4229128391509456</v>
       </c>
       <c r="D2030">
         <v>13.81643391745308</v>
@@ -80718,10 +80706,10 @@
         <v>16.46412481632129</v>
       </c>
       <c r="F2030">
-        <v>93.42374689435385</v>
+        <v>93.32822423376351</v>
       </c>
       <c r="G2030">
-        <v>38.93983342365495</v>
+        <v>38.94239220520944</v>
       </c>
       <c r="H2030">
         <v>20.37670663697891</v>
@@ -80730,13 +80718,13 @@
         <v>3.264714165210502</v>
       </c>
       <c r="J2030">
-        <v>59.35577946001091</v>
+        <v>59.35948623266186</v>
       </c>
       <c r="K2030">
-        <v>77.7371368843764</v>
+        <v>77.74224170368785</v>
       </c>
       <c r="L2030">
-        <v>95.7096987446477</v>
+        <v>95.71535775324949</v>
       </c>
     </row>
     <row r="2031" spans="1:12">
@@ -80747,7 +80735,7 @@
         <v>2.105279420821739</v>
       </c>
       <c r="C2031">
-        <v>0.4146068884760908</v>
+        <v>0.4147860520515979</v>
       </c>
       <c r="D2031">
         <v>13.5931903115552</v>
@@ -80756,10 +80744,10 @@
         <v>16.19810026802556</v>
       </c>
       <c r="F2031">
-        <v>92.48100306645345</v>
+        <v>92.38644432993691</v>
       </c>
       <c r="G2031">
-        <v>38.37588381187462</v>
+        <v>38.37840553564696</v>
       </c>
       <c r="H2031">
         <v>20.44177690431112</v>
@@ -80768,13 +80756,13 @@
         <v>3.270542320845658</v>
       </c>
       <c r="J2031">
-        <v>58.58652152803634</v>
+        <v>58.5901802604747</v>
       </c>
       <c r="K2031">
-        <v>76.6806898881334</v>
+        <v>76.68572533299599</v>
       </c>
       <c r="L2031">
-        <v>94.61548319536581</v>
+        <v>94.62107750649926</v>
       </c>
     </row>
     <row r="2032" spans="1:12">
@@ -80785,7 +80773,7 @@
         <v>2.125753499904209</v>
       </c>
       <c r="C2032">
-        <v>0.4192739193496069</v>
+        <v>0.4194550996835461</v>
       </c>
       <c r="D2032">
         <v>13.65288367040754</v>
@@ -80794,10 +80782,10 @@
         <v>16.26923287117931</v>
       </c>
       <c r="F2032">
-        <v>92.05592258806023</v>
+        <v>91.96179848213391</v>
       </c>
       <c r="G2032">
-        <v>38.434281698155</v>
+        <v>38.43680725932008</v>
       </c>
       <c r="H2032">
         <v>20.29655096539537</v>
@@ -80806,13 +80794,13 @@
         <v>3.277826724661287</v>
       </c>
       <c r="J2032">
-        <v>58.56716189740849</v>
+        <v>58.57081942083654</v>
       </c>
       <c r="K2032">
-        <v>76.88277206924229</v>
+        <v>76.88782078437778</v>
       </c>
       <c r="L2032">
-        <v>94.67184969205552</v>
+        <v>94.67744733595977</v>
       </c>
     </row>
     <row r="2033" spans="1:12">
@@ -80823,7 +80811,7 @@
         <v>2.061646137531231</v>
       </c>
       <c r="C2033">
-        <v>0.4053726797195336</v>
+        <v>0.4055478529275293</v>
       </c>
       <c r="D2033">
         <v>13.25354808739207</v>
@@ -80832,10 +80820,10 @@
         <v>15.79337123266636</v>
       </c>
       <c r="F2033">
-        <v>91.74107362584523</v>
+        <v>91.64727144246596</v>
       </c>
       <c r="G2033">
-        <v>37.64968397650438</v>
+        <v>37.65215798084444</v>
       </c>
       <c r="H2033">
         <v>20.3725458391674</v>
@@ -80844,13 +80832,13 @@
         <v>3.268277392406751</v>
       </c>
       <c r="J2033">
-        <v>57.48617310197307</v>
+        <v>57.48976311757392</v>
       </c>
       <c r="K2033">
-        <v>75.20129481495562</v>
+        <v>75.20623311134013</v>
       </c>
       <c r="L2033">
-        <v>92.89698532217176</v>
+        <v>92.90247802401824</v>
       </c>
     </row>
     <row r="2034" spans="1:12">
@@ -80861,7 +80849,7 @@
         <v>2.065349490368891</v>
       </c>
       <c r="C2034">
-        <v>0.4067882941348118</v>
+        <v>0.4069640790705604</v>
       </c>
       <c r="D2034">
         <v>13.33301290370189</v>
@@ -80870,10 +80858,10 @@
         <v>15.88859061159028</v>
       </c>
       <c r="F2034">
-        <v>92.43676424898223</v>
+        <v>92.3422507451787</v>
       </c>
       <c r="G2034">
-        <v>37.98435788806964</v>
+        <v>37.98685388422005</v>
       </c>
       <c r="H2034">
         <v>20.43901967282306</v>
@@ -80882,13 +80870,13 @@
         <v>3.259859643636875</v>
       </c>
       <c r="J2034">
-        <v>58.01851956826415</v>
+        <v>58.02214282893971</v>
       </c>
       <c r="K2034">
-        <v>75.77292692787512</v>
+        <v>75.77790276202813</v>
       </c>
       <c r="L2034">
-        <v>93.6082930888104</v>
+        <v>93.61382784801181</v>
       </c>
     </row>
     <row r="2035" spans="1:12">
@@ -80899,7 +80887,7 @@
         <v>2.074044349492612</v>
       </c>
       <c r="C2035">
-        <v>0.4129427398556225</v>
+        <v>0.4131211843045901</v>
       </c>
       <c r="D2035">
         <v>13.55411727670521</v>
@@ -80908,10 +80896,10 @@
         <v>16.15101705832825</v>
       </c>
       <c r="F2035">
-        <v>92.96637276683754</v>
+        <v>92.87131775601489</v>
       </c>
       <c r="G2035">
-        <v>38.55671624505734</v>
+        <v>38.5592498515383</v>
       </c>
       <c r="H2035">
         <v>20.57800701334016</v>
@@ -80920,13 +80908,13 @@
         <v>3.255619839075363</v>
       </c>
       <c r="J2035">
-        <v>58.94767896237158</v>
+        <v>58.95136024911742</v>
       </c>
       <c r="K2035">
-        <v>76.86541794773701</v>
+        <v>76.87046552326717</v>
       </c>
       <c r="L2035">
-        <v>94.98210603685365</v>
+        <v>94.98772202522403</v>
       </c>
     </row>
     <row r="2036" spans="1:12">
@@ -80937,7 +80925,7 @@
         <v>2.064916337289424</v>
       </c>
       <c r="C2036">
-        <v>0.4138113532034738</v>
+        <v>0.4139901730052815</v>
       </c>
       <c r="D2036">
         <v>13.63605797467123</v>
@@ -80946,10 +80934,10 @@
         <v>16.24865717635314</v>
       </c>
       <c r="F2036">
-        <v>93.80709623398934</v>
+        <v>93.711181611504</v>
       </c>
       <c r="G2036">
-        <v>38.80001743400147</v>
+        <v>38.80256702808534</v>
       </c>
       <c r="H2036">
         <v>20.55920016755862</v>
@@ -80958,13 +80946,13 @@
         <v>3.249453326385535</v>
       </c>
       <c r="J2036">
-        <v>59.28758438830683</v>
+        <v>59.2912869021707</v>
       </c>
       <c r="K2036">
-        <v>77.27765939692694</v>
+        <v>77.28273404340665</v>
       </c>
       <c r="L2036">
-        <v>95.41886801514042</v>
+        <v>95.4245098278507</v>
       </c>
     </row>
     <row r="2037" spans="1:12">
@@ -80975,7 +80963,7 @@
         <v>2.071371943380795</v>
       </c>
       <c r="C2037">
-        <v>0.4146147540835701</v>
+        <v>0.4147939210580327</v>
       </c>
       <c r="D2037">
         <v>13.55964132872468</v>
@@ -80984,10 +80972,10 @@
         <v>16.15759949055725</v>
       </c>
       <c r="F2037">
-        <v>92.98399629067863</v>
+        <v>92.88892326039162</v>
       </c>
       <c r="G2037">
-        <v>38.57817692305164</v>
+        <v>38.5807119397386</v>
       </c>
       <c r="H2037">
         <v>20.57903707202879</v>
@@ -80996,13 +80984,13 @@
         <v>3.243926906277795</v>
       </c>
       <c r="J2037">
-        <v>58.9798555802354</v>
+        <v>58.98353887641331</v>
       </c>
       <c r="K2037">
-        <v>76.77010762098078</v>
+        <v>76.77514893770059</v>
       </c>
       <c r="L2037">
-        <v>94.87785341322139</v>
+        <v>94.88346323746732</v>
       </c>
     </row>
     <row r="2038" spans="1:12">
@@ -81013,7 +81001,7 @@
         <v>2.074110771008876</v>
       </c>
       <c r="C2038">
-        <v>0.4182896546822369</v>
+        <v>0.4184704096870704</v>
       </c>
       <c r="D2038">
         <v>13.68628188852085</v>
@@ -81022,10 +81010,10 @@
         <v>16.30850373609298</v>
       </c>
       <c r="F2038">
-        <v>93.43356883578349</v>
+        <v>93.33803613258607</v>
       </c>
       <c r="G2038">
-        <v>38.81439051156624</v>
+        <v>38.81694105012168</v>
       </c>
       <c r="H2038">
         <v>20.63120623984336</v>
@@ -81034,13 +81022,13 @@
         <v>3.241715069541287</v>
       </c>
       <c r="J2038">
-        <v>59.36031111927787</v>
+        <v>59.36401817493127</v>
       </c>
       <c r="K2038">
-        <v>77.213997381403</v>
+        <v>77.21906784734431</v>
       </c>
       <c r="L2038">
-        <v>95.43171469434805</v>
+        <v>95.43735726664141</v>
       </c>
     </row>
     <row r="2039" spans="1:12">
@@ -81051,7 +81039,7 @@
         <v>2.069036591133425</v>
       </c>
       <c r="C2039">
-        <v>0.4146027246846228</v>
+        <v>0.4147818864608359</v>
       </c>
       <c r="D2039">
         <v>13.51653927438803</v>
@@ -81060,10 +81048,10 @@
         <v>16.10623930231121</v>
       </c>
       <c r="F2039">
-        <v>92.42284437114473</v>
+        <v>92.32834509995143</v>
       </c>
       <c r="G2039">
-        <v>38.24041676941754</v>
+        <v>38.24292959149361</v>
       </c>
       <c r="H2039">
         <v>20.37233701508507</v>
@@ -81072,13 +81060,13 @@
         <v>3.261142002496045</v>
       </c>
       <c r="J2039">
-        <v>58.34019614007112</v>
+        <v>58.34383948947147</v>
       </c>
       <c r="K2039">
-        <v>76.30354739164646</v>
+        <v>76.30855807042714</v>
       </c>
       <c r="L2039">
-        <v>94.119624522313</v>
+        <v>94.12518951490789</v>
       </c>
     </row>
     <row r="2040" spans="1:12">
@@ -81089,7 +81077,7 @@
         <v>2.065585498735192</v>
       </c>
       <c r="C2040">
-        <v>0.4092977581861682</v>
+        <v>0.4094746275335958</v>
       </c>
       <c r="D2040">
         <v>13.44083104191122</v>
@@ -81098,10 +81086,10 @@
         <v>16.01709950768173</v>
       </c>
       <c r="F2040">
-        <v>92.88404797156127</v>
+        <v>92.78907713509201</v>
       </c>
       <c r="G2040">
-        <v>38.26524270935565</v>
+        <v>38.26775716277299</v>
       </c>
       <c r="H2040">
         <v>20.47070790183667</v>
@@ -81110,13 +81098,13 @@
         <v>3.280927876566561</v>
       </c>
       <c r="J2040">
-        <v>58.44660334963874</v>
+        <v>58.4502533441769</v>
       </c>
       <c r="K2040">
-        <v>76.58455713541267</v>
+        <v>76.58958626745809</v>
       </c>
       <c r="L2040">
-        <v>94.54520251693226</v>
+        <v>94.55079267259383</v>
       </c>
     </row>
     <row r="2041" spans="1:12">
@@ -81124,22 +81112,22 @@
         <v>45139</v>
       </c>
       <c r="B2041">
-        <v>2.039207677435845</v>
+        <v>2.099060529708546</v>
       </c>
       <c r="C2041">
-        <v>0.4063054548310456</v>
+        <v>0.4143728242556954</v>
       </c>
       <c r="D2041">
-        <v>13.32659501359058</v>
+        <v>13.56080289581537</v>
       </c>
       <c r="E2041">
-        <v>15.87875099516235</v>
+        <v>16.14820483597503</v>
       </c>
       <c r="F2041">
-        <v>92.69304070886537</v>
+        <v>92.4970482607897</v>
       </c>
       <c r="G2041">
-        <v>38.26524270935565</v>
+        <v>38.26775716277299</v>
       </c>
       <c r="H2041">
         <v>20.57282260367525</v>
@@ -81148,13 +81136,13 @@
         <v>3.287041496226271</v>
       </c>
       <c r="J2041">
-        <v>58.51949112546878</v>
+        <v>58.52314567185372</v>
       </c>
       <c r="K2041">
-        <v>76.65591025132194</v>
+        <v>76.66094406896268</v>
       </c>
       <c r="L2041">
-        <v>94.7423864416924</v>
+        <v>94.74798825620925</v>
       </c>
     </row>
   </sheetData>
@@ -81169,49 +81157,49 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="B1" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -81496,10 +81484,10 @@
         <v>-0.04068489104751771</v>
       </c>
       <c r="K7">
-        <v>-0.01277014256514608</v>
+        <v>0.01620607377126326</v>
       </c>
       <c r="P7">
-        <v>0.7445443224683275</v>
+        <v>0.7957485008221337</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -81769,25 +81757,25 @@
         <v>-0.009579543437776339</v>
       </c>
       <c r="F13">
-        <v>0.001242272064002181</v>
+        <v>0.001674937681476418</v>
       </c>
       <c r="G13">
-        <v>-0.03244369855762419</v>
+        <v>-0.03244369855762452</v>
       </c>
       <c r="H13">
-        <v>-0.07238972564448165</v>
+        <v>-0.07238972564448132</v>
       </c>
       <c r="I13">
-        <v>0.03408271391997597</v>
+        <v>0.03408271391997642</v>
       </c>
       <c r="J13">
-        <v>0.07131604906078404</v>
+        <v>0.0713160490607847</v>
       </c>
       <c r="K13">
-        <v>-0.007310822733022415</v>
+        <v>0.01196214952707364</v>
       </c>
       <c r="P13">
-        <v>0.464129149504406</v>
+        <v>0.4932000630105069</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -82072,10 +82060,10 @@
         <v>-0.007038508238649044</v>
       </c>
       <c r="K19">
-        <v>-0.008499178954369135</v>
+        <v>0.008925925304026805</v>
       </c>
       <c r="P19">
-        <v>0.2812602820528733</v>
+        <v>0.3037777560912389</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -82360,10 +82348,10 @@
         <v>-0.01058438652620775</v>
       </c>
       <c r="K25">
-        <v>-0.008637550915696401</v>
+        <v>0.008185335193205301</v>
       </c>
       <c r="P25">
-        <v>0.2058428651547837</v>
+        <v>0.2263053682528868</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -82633,25 +82621,25 @@
         <v>-0.0747807021862984</v>
       </c>
       <c r="F31">
-        <v>-0.08687979517704725</v>
+        <v>-0.08781343008576048</v>
       </c>
       <c r="G31">
-        <v>-0.1487690436391113</v>
+        <v>-0.1487690436391114</v>
       </c>
       <c r="H31">
-        <v>0.003383032757908522</v>
+        <v>0.003383032757908744</v>
       </c>
       <c r="I31">
-        <v>0.2841372678622063</v>
+        <v>0.2841372678622061</v>
       </c>
       <c r="J31">
-        <v>-0.1867093196123172</v>
+        <v>-0.1867093196123188</v>
       </c>
       <c r="K31">
-        <v>-0.00205640545246677</v>
+        <v>-0.003147233309338304</v>
       </c>
       <c r="P31">
-        <v>-0.1436419345886649</v>
+        <v>-0.1454526391721568</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -82921,25 +82909,25 @@
         <v>-0.06599477974804902</v>
       </c>
       <c r="F37">
-        <v>0.02576142571500961</v>
+        <v>0.02582882968633338</v>
       </c>
       <c r="G37">
         <v>-0.1489795562888799</v>
       </c>
       <c r="H37">
-        <v>-0.03162595423183434</v>
+        <v>-0.03162595423183479</v>
       </c>
       <c r="I37">
-        <v>0.2239596164186992</v>
+        <v>0.223959616418699</v>
       </c>
       <c r="J37">
-        <v>-0.03540237364130561</v>
+        <v>-0.03540237364130572</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>0.242926525561028</v>
+        <v>0.243008199702583</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -83785,25 +83773,25 @@
         <v>-0.06696089365091384</v>
       </c>
       <c r="F55">
-        <v>0.032789878770904</v>
+        <v>0.0328543765723246</v>
       </c>
       <c r="G55">
-        <v>-0.1359898026255569</v>
+        <v>-0.1359898026255572</v>
       </c>
       <c r="H55">
-        <v>0.005242254440698702</v>
+        <v>0.005242254440697813</v>
       </c>
       <c r="I55">
-        <v>0.2024891428246725</v>
+        <v>0.202489142824674</v>
       </c>
       <c r="J55">
-        <v>-0.03438924769001739</v>
+        <v>-0.03438924769001728</v>
       </c>
       <c r="K55">
         <v>0.00124708317768274</v>
       </c>
       <c r="P55">
-        <v>0.2701723886816212</v>
+        <v>0.2702517110376776</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -84073,25 +84061,25 @@
         <v>-0.07917535906922624</v>
       </c>
       <c r="F61">
-        <v>0.117971909067222</v>
+        <v>0.1180453237158694</v>
       </c>
       <c r="G61">
-        <v>-0.121062731792381</v>
+        <v>-0.1210627317923809</v>
       </c>
       <c r="H61">
-        <v>-0.04210076665417095</v>
+        <v>-0.04210076665417262</v>
       </c>
       <c r="I61">
-        <v>0.3288180500205955</v>
+        <v>0.3288180500205951</v>
       </c>
       <c r="J61">
-        <v>-0.08204255756808299</v>
+        <v>-0.08204255756808287</v>
       </c>
       <c r="K61">
         <v>0.0009316906511989131</v>
       </c>
       <c r="P61">
-        <v>0.4267691903317474</v>
+        <v>0.4268628829889214</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -84361,25 +84349,25 @@
         <v>-0.07535945697019852</v>
       </c>
       <c r="F67">
-        <v>0.1150896569014164</v>
+        <v>0.1151555885890418</v>
       </c>
       <c r="G67">
-        <v>-0.1030921246564235</v>
+        <v>-0.1030921246564237</v>
       </c>
       <c r="H67">
-        <v>-0.002692400536646433</v>
+        <v>-0.002692400536648321</v>
       </c>
       <c r="I67">
-        <v>0.2822384480450766</v>
+        <v>0.2822384480450773</v>
       </c>
       <c r="J67">
-        <v>-0.07491475840989037</v>
+        <v>-0.07491475840989004</v>
       </c>
       <c r="K67">
         <v>0.00208560476376185</v>
       </c>
       <c r="P67">
-        <v>0.4261056977984117</v>
+        <v>0.4261900188705374</v>
       </c>
     </row>
   </sheetData>
